--- a/laser time calibration/messprotokoll.xlsx
+++ b/laser time calibration/messprotokoll.xlsx
@@ -5,23 +5,29 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Arbeit\LaserTimeCalibration\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vince\Documents\GitHub\ChronoSlicer\laser time calibration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4797CA7F-D1C7-4E71-B142-A6B664FAE1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC1ECF31-406D-41BE-AA1C-C5E7038542EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Messprotokoll" sheetId="1" r:id="rId1"/>
-    <sheet name="Legende" sheetId="2" r:id="rId2"/>
+    <sheet name="Messprotokoll Real" sheetId="4" r:id="rId2"/>
+    <sheet name="Legende" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="235">
   <si>
     <t>file</t>
   </si>
@@ -467,9 +473,6 @@
     <t>--&gt;</t>
   </si>
   <si>
-    <t>01:12</t>
-  </si>
-  <si>
     <t>preset</t>
   </si>
   <si>
@@ -522,6 +525,213 @@
   </si>
   <si>
     <t>relative Abweichung</t>
+  </si>
+  <si>
+    <t>dpi - 1 sweap = 1 dot</t>
+  </si>
+  <si>
+    <t>54_rast_overscan</t>
+  </si>
+  <si>
+    <t>55_rast_speed</t>
+  </si>
+  <si>
+    <t>06:19</t>
+  </si>
+  <si>
+    <t>--- 3. MESSREIHE (noch zu messen) ---</t>
+  </si>
+  <si>
+    <t>A: Zeilen-Overhead 10 %</t>
+  </si>
+  <si>
+    <t>A: Zeilen-Overhead 20 %</t>
+  </si>
+  <si>
+    <t>A: Zeilen-Overhead 40 %</t>
+  </si>
+  <si>
+    <t>A: Zeilen-Overhead 60 %</t>
+  </si>
+  <si>
+    <t>A: Zeilen-Overhead 80 %</t>
+  </si>
+  <si>
+    <t>A: Rastergeschw. 10 %</t>
+  </si>
+  <si>
+    <t>v = 200*999/(Zeile91-Zeile86)</t>
+  </si>
+  <si>
+    <t>A: Rastergeschw. 20 %</t>
+  </si>
+  <si>
+    <t>v = 200*999/(Zeile92-Zeile87)</t>
+  </si>
+  <si>
+    <t>A: Rastergeschw. 40 %</t>
+  </si>
+  <si>
+    <t>v = 200*999/(Zeile93-Zeile88)</t>
+  </si>
+  <si>
+    <t>A: Rastergeschw. 60 %</t>
+  </si>
+  <si>
+    <t>v = 200*999/(Zeile94-Zeile89)</t>
+  </si>
+  <si>
+    <t>A: Rastergeschw. 80 %</t>
+  </si>
+  <si>
+    <t>v = 200*999/(Zeile95-Zeile90)</t>
+  </si>
+  <si>
+    <t>A: haengt v_raster an der Aufloesung?</t>
+  </si>
+  <si>
+    <t>wie Zeile 74, nur 600 statt 200 dpi</t>
+  </si>
+  <si>
+    <t>v = 600*999/(Zeile97-Zeile96); ist v != 1820, bremst hohe dpi das Raster</t>
+  </si>
+  <si>
+    <t>A: 80 %-Anzeige nachlesen</t>
+  </si>
+  <si>
+    <t>notiert sind 334 s (5:34); linear zu erwarten waeren 314 s (5:14)</t>
+  </si>
+  <si>
+    <t>56_vecstart_400</t>
+  </si>
+  <si>
+    <t>B: Startaufwand je Vektor, 400 Konturen</t>
+  </si>
+  <si>
+    <t>mit Zeile 64 (200) und 100 (800): (t-Schnittzeit)/n muss konstant sein</t>
+  </si>
+  <si>
+    <t>57_vecstart_800</t>
+  </si>
+  <si>
+    <t>B: Startaufwand je Vektor, 800 Konturen</t>
+  </si>
+  <si>
+    <t>800 Konturen = Groessenordnung realer Dateien</t>
+  </si>
+  <si>
+    <t>58_order_big</t>
+  </si>
+  <si>
+    <t>B: Pfadreihenfolge bei 300 Konturen</t>
+  </si>
+  <si>
+    <t>Modell: greedy-nn 117,5 s, 2-opt 105,9 s - die Anzeige entscheidet</t>
+  </si>
+  <si>
+    <t>59_zigzag_n48</t>
+  </si>
+  <si>
+    <t>C: Nachbar von n=64 (Segment 5,42 mm)</t>
+  </si>
+  <si>
+    <t>n=64 zeigt 181 s statt 150 s - schmaler Ausreisser oder ganzes Band?</t>
+  </si>
+  <si>
+    <t>60_zigzag_n80</t>
+  </si>
+  <si>
+    <t>C: Nachbar von n=64 (Segment 5,15 mm)</t>
+  </si>
+  <si>
+    <t>8/100</t>
+  </si>
+  <si>
+    <t>D: Validierung Raster 100 % im Mischjob</t>
+  </si>
+  <si>
+    <t>wie Zeile 35, aber Raster 100 % statt 20 % - nicht mitfitten</t>
+  </si>
+  <si>
+    <t>--- ANZEIGE GEGEN REALITAET (Stoppuhr) ---</t>
+  </si>
+  <si>
+    <t>hier meas E / opt_meas E fuellen, est E ist schon bekannt</t>
+  </si>
+  <si>
+    <t>E: reiner Vektor</t>
+  </si>
+  <si>
+    <t>Anzeige 100 s</t>
+  </si>
+  <si>
+    <t>E: leerwegdominiert</t>
+  </si>
+  <si>
+    <t>Anzeige 146 s</t>
+  </si>
+  <si>
+    <t>E: Raster langsam</t>
+  </si>
+  <si>
+    <t>Anzeige 224 s</t>
+  </si>
+  <si>
+    <t>E: Raster bei 100 %</t>
+  </si>
+  <si>
+    <t>Anzeige 300 s - der neu vermessene Bereich</t>
+  </si>
+  <si>
+    <t>E: Kurven</t>
+  </si>
+  <si>
+    <t>Anzeige 145 s</t>
+  </si>
+  <si>
+    <t>--- GEORGE (120 W) ---</t>
+  </si>
+  <si>
+    <t>hier est G / opt_est G fuellen; die D-Spalten rechnen gegen Edgar</t>
+  </si>
+  <si>
+    <t>F: George, Vektor</t>
+  </si>
+  <si>
+    <t>F: George, Ecken</t>
+  </si>
+  <si>
+    <t>F: George, Raster 20 %</t>
+  </si>
+  <si>
+    <t>F: George, Raster breit</t>
+  </si>
+  <si>
+    <t>F: George, Raster hoch</t>
+  </si>
+  <si>
+    <t>F: George, Raster 100 %</t>
+  </si>
+  <si>
+    <t>wichtigster George-Lauf: prueft die neue Rastertabelle</t>
+  </si>
+  <si>
+    <t>--- REIHENFOLGE DIREKT ABLESEN (Video) ---</t>
+  </si>
+  <si>
+    <t>beobachtete Zahlenfolge hier eintragen</t>
+  </si>
+  <si>
+    <t>61_order_numbers</t>
+  </si>
+  <si>
+    <t>G: welche Tour faehrt die Maschine?</t>
+  </si>
+  <si>
+    <t>25 lesbare Zahlen, mit 'Optimieren' laufen lassen und filmen; die Reihenfolge der Zahlen notieren. Ohne 'Optimieren' muss 1,2,3,...,25 herauskommen - guter Gegencheck.</t>
+  </si>
+  <si>
+    <t>ChronoCut auf der bereinigten Datei (weiss entfernt, schwarz-&gt;blau). Preset unsicher ('MDF_3_0mm ?'): mit dessen 7 % Schnittgeschwindigkeit kaeme ein Vielfaches der abgelesenen 323 s heraus - ohne gesichertes Preset nicht als Validierung nutzbar.</t>
   </si>
 </sst>
 </file>
@@ -530,9 +740,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="#,##0\ &quot;s&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0\ &quot;s&quot;"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -568,6 +778,14 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -626,7 +844,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -651,10 +869,11 @@
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -957,16 +1176,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE104"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AE116"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="7.6640625" customWidth="1"/>
     <col min="3" max="3" width="7.44140625" customWidth="1"/>
     <col min="4" max="4" width="8.109375" customWidth="1"/>
     <col min="5" max="5" width="8.5546875" customWidth="1"/>
-    <col min="6" max="22" width="12.77734375" customWidth="1"/>
-    <col min="23" max="23" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="22" width="12.6640625" customWidth="1"/>
+    <col min="23" max="23" width="24.6640625" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="26.5546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14" bestFit="1" customWidth="1"/>
@@ -991,7 +1210,7 @@
         <v>144</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>2</v>
@@ -1087,22 +1306,22 @@
         <v>1</v>
       </c>
       <c r="Q2" s="1">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="R2" s="1">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="S2" s="1">
         <f t="shared" ref="S2:S48" si="0">IF(AND(ISNUMBER(Q2),ISNUMBER(G2)),Q2-G2,"")</f>
-        <v>0</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="T2" s="1">
         <f t="shared" ref="T2:T48" si="1">IF(AND(ISNUMBER(R2),ISNUMBER(I2)),R2-I2,"")</f>
-        <v>0</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="U2" s="9">
         <f t="shared" ref="U2:U48" si="2">IF(AND(ISNUMBER(R2),ISNUMBER(I2),I2&lt;&gt;0),(R2-I2)/I2,"")</f>
-        <v>0</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="W2" s="1">
         <v>3.14</v>
@@ -1147,22 +1366,22 @@
         <v>1</v>
       </c>
       <c r="Q3" s="1">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="R3" s="1">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S3" s="1">
         <f t="shared" si="0"/>
-        <v>0.30000000000000004</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="T3" s="1">
         <f t="shared" si="1"/>
-        <v>0.30000000000000004</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="U3" s="9">
         <f t="shared" si="2"/>
-        <v>0.30000000000000004</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="W3" s="1">
         <v>10</v>
@@ -1201,22 +1420,22 @@
         <v>26</v>
       </c>
       <c r="Q4" s="1">
-        <v>26</v>
+        <v>25.8</v>
       </c>
       <c r="R4" s="1">
-        <v>26</v>
+        <v>25.8</v>
       </c>
       <c r="S4" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-0.19999999999999929</v>
       </c>
       <c r="T4" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-0.19999999999999929</v>
       </c>
       <c r="U4" s="9">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-7.692307692307665E-3</v>
       </c>
       <c r="W4" s="1">
         <v>500</v>
@@ -1257,22 +1476,22 @@
         <v>51</v>
       </c>
       <c r="Q5" s="1">
-        <v>50.8</v>
+        <v>50.3</v>
       </c>
       <c r="R5" s="1">
-        <v>50.8</v>
+        <v>50.3</v>
       </c>
       <c r="S5" s="1">
         <f t="shared" si="0"/>
-        <v>-0.20000000000000284</v>
+        <v>-0.70000000000000284</v>
       </c>
       <c r="T5" s="1">
         <f t="shared" si="1"/>
-        <v>-0.20000000000000284</v>
+        <v>-0.70000000000000284</v>
       </c>
       <c r="U5" s="9">
         <f t="shared" si="2"/>
-        <v>-3.9215686274510358E-3</v>
+        <v>-1.3725490196078487E-2</v>
       </c>
       <c r="W5" s="1">
         <v>1000</v>
@@ -1313,22 +1532,22 @@
         <v>100</v>
       </c>
       <c r="Q6" s="1">
-        <v>100.4</v>
+        <v>99.3</v>
       </c>
       <c r="R6" s="1">
-        <v>100.4</v>
+        <v>99.3</v>
       </c>
       <c r="S6" s="1">
         <f t="shared" si="0"/>
-        <v>0.40000000000000568</v>
+        <v>-0.70000000000000284</v>
       </c>
       <c r="T6" s="1">
         <f t="shared" si="1"/>
-        <v>0.40000000000000568</v>
+        <v>-0.70000000000000284</v>
       </c>
       <c r="U6" s="9">
         <f t="shared" si="2"/>
-        <v>4.0000000000000565E-3</v>
+        <v>-7.0000000000000288E-3</v>
       </c>
       <c r="W6" s="1">
         <v>2000</v>
@@ -1369,22 +1588,22 @@
         <v>174</v>
       </c>
       <c r="Q7" s="1">
-        <v>174.8</v>
+        <v>172.8</v>
       </c>
       <c r="R7" s="1">
-        <v>174.8</v>
+        <v>172.8</v>
       </c>
       <c r="S7" s="1">
         <f t="shared" si="0"/>
-        <v>0.80000000000001137</v>
+        <v>-1.1999999999999886</v>
       </c>
       <c r="T7" s="1">
         <f t="shared" si="1"/>
-        <v>0.80000000000001137</v>
+        <v>-1.1999999999999886</v>
       </c>
       <c r="U7" s="9">
         <f t="shared" si="2"/>
-        <v>4.5977011494253523E-3</v>
+        <v>-6.8965517241378659E-3</v>
       </c>
       <c r="W7" s="1">
         <v>3500</v>
@@ -1425,22 +1644,22 @@
         <v>248</v>
       </c>
       <c r="Q8" s="1">
-        <v>249.2</v>
+        <v>246.4</v>
       </c>
       <c r="R8" s="1">
-        <v>249.2</v>
+        <v>246.4</v>
       </c>
       <c r="S8" s="1">
         <f t="shared" si="0"/>
-        <v>1.1999999999999886</v>
+        <v>-1.5999999999999943</v>
       </c>
       <c r="T8" s="1">
         <f t="shared" si="1"/>
-        <v>1.1999999999999886</v>
+        <v>-1.5999999999999943</v>
       </c>
       <c r="U8" s="9">
         <f t="shared" si="2"/>
-        <v>4.8387096774193091E-3</v>
+        <v>-6.4516129032257839E-3</v>
       </c>
       <c r="W8" s="1">
         <v>5000</v>
@@ -1481,22 +1700,22 @@
         <v>44</v>
       </c>
       <c r="Q9" s="1">
-        <v>45.1</v>
+        <v>44.3</v>
       </c>
       <c r="R9" s="1">
-        <v>45.1</v>
+        <v>44.3</v>
       </c>
       <c r="S9" s="1">
         <f t="shared" si="0"/>
-        <v>0.10000000000000142</v>
+        <v>-0.70000000000000284</v>
       </c>
       <c r="T9" s="1">
         <f t="shared" si="1"/>
-        <v>1.1000000000000014</v>
+        <v>0.29999999999999716</v>
       </c>
       <c r="U9" s="9">
         <f t="shared" si="2"/>
-        <v>2.5000000000000033E-2</v>
+        <v>6.8181818181817537E-3</v>
       </c>
       <c r="W9" s="1">
         <v>871.84</v>
@@ -1537,22 +1756,22 @@
         <v>48</v>
       </c>
       <c r="Q10" s="1">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="R10" s="1">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="S10" s="1">
         <f t="shared" si="0"/>
-        <v>0.29999999999999716</v>
+        <v>0.20000000000000284</v>
       </c>
       <c r="T10" s="1">
         <f t="shared" si="1"/>
-        <v>0.29999999999999716</v>
+        <v>0.20000000000000284</v>
       </c>
       <c r="U10" s="9">
         <f t="shared" si="2"/>
-        <v>6.2499999999999405E-3</v>
+        <v>4.1666666666667256E-3</v>
       </c>
       <c r="W10" s="1">
         <v>917.63</v>
@@ -1593,22 +1812,22 @@
         <v>58</v>
       </c>
       <c r="Q11" s="1">
-        <v>58.2</v>
+        <v>58.1</v>
       </c>
       <c r="R11" s="1">
-        <v>58.2</v>
+        <v>58.1</v>
       </c>
       <c r="S11" s="1">
         <f t="shared" si="0"/>
-        <v>0.20000000000000284</v>
+        <v>0.10000000000000142</v>
       </c>
       <c r="T11" s="1">
         <f t="shared" si="1"/>
-        <v>0.20000000000000284</v>
+        <v>0.10000000000000142</v>
       </c>
       <c r="U11" s="9">
         <f t="shared" si="2"/>
-        <v>3.4482758620690145E-3</v>
+        <v>1.7241379310345072E-3</v>
       </c>
       <c r="W11" s="1">
         <v>1080.5</v>
@@ -1649,22 +1868,22 @@
         <v>86</v>
       </c>
       <c r="Q12" s="1">
-        <v>85.8</v>
+        <v>85.6</v>
       </c>
       <c r="R12" s="1">
-        <v>85.8</v>
+        <v>85.6</v>
       </c>
       <c r="S12" s="1">
         <f t="shared" si="0"/>
-        <v>-0.20000000000000284</v>
+        <v>-0.40000000000000568</v>
       </c>
       <c r="T12" s="1">
         <f t="shared" si="1"/>
-        <v>-0.20000000000000284</v>
+        <v>-0.40000000000000568</v>
       </c>
       <c r="U12" s="9">
         <f t="shared" si="2"/>
-        <v>-2.3255813953488701E-3</v>
+        <v>-4.6511627906977403E-3</v>
       </c>
       <c r="W12" s="1">
         <v>1565.44</v>
@@ -1705,22 +1924,22 @@
         <v>181</v>
       </c>
       <c r="Q13" s="1">
-        <v>151</v>
+        <v>150.5</v>
       </c>
       <c r="R13" s="1">
-        <v>151</v>
+        <v>150.5</v>
       </c>
       <c r="S13" s="1">
         <f t="shared" si="0"/>
-        <v>-29</v>
+        <v>-29.5</v>
       </c>
       <c r="T13" s="1">
         <f t="shared" si="1"/>
-        <v>-30</v>
+        <v>-30.5</v>
       </c>
       <c r="U13" s="9">
         <f t="shared" si="2"/>
-        <v>-0.16574585635359115</v>
+        <v>-0.16850828729281769</v>
       </c>
       <c r="W13" s="1">
         <v>2738.09</v>
@@ -1761,22 +1980,22 @@
         <v>289</v>
       </c>
       <c r="Q14" s="1">
-        <v>289.5</v>
+        <v>288.2</v>
       </c>
       <c r="R14" s="1">
-        <v>289.5</v>
+        <v>288.2</v>
       </c>
       <c r="S14" s="1">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>0.19999999999998863</v>
       </c>
       <c r="T14" s="1">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>-0.80000000000001137</v>
       </c>
       <c r="U14" s="9">
         <f t="shared" si="2"/>
-        <v>1.7301038062283738E-3</v>
+        <v>-2.7681660899654373E-3</v>
       </c>
       <c r="W14" s="1">
         <v>5238.12</v>
@@ -1817,22 +2036,22 @@
         <v>145</v>
       </c>
       <c r="Q15" s="1">
-        <v>145.30000000000001</v>
+        <v>144.1</v>
       </c>
       <c r="R15" s="1">
-        <v>145.30000000000001</v>
+        <v>144.1</v>
       </c>
       <c r="S15" s="1">
         <f t="shared" si="0"/>
-        <v>-23.699999999999989</v>
+        <v>-24.900000000000006</v>
       </c>
       <c r="T15" s="1">
         <f t="shared" si="1"/>
-        <v>0.30000000000001137</v>
+        <v>-0.90000000000000568</v>
       </c>
       <c r="U15" s="9">
         <f t="shared" si="2"/>
-        <v>2.0689655172414579E-3</v>
+        <v>-6.2068965517241767E-3</v>
       </c>
       <c r="W15" s="1">
         <v>2893.9</v>
@@ -1871,22 +2090,22 @@
         <v>145</v>
       </c>
       <c r="Q16" s="1">
-        <v>147.19999999999999</v>
+        <v>146.1</v>
       </c>
       <c r="R16" s="1">
-        <v>147.19999999999999</v>
+        <v>146.1</v>
       </c>
       <c r="S16" s="1">
         <f t="shared" si="0"/>
-        <v>1.1999999999999886</v>
+        <v>9.9999999999994316E-2</v>
       </c>
       <c r="T16" s="1">
         <f t="shared" si="1"/>
-        <v>2.1999999999999886</v>
+        <v>1.0999999999999943</v>
       </c>
       <c r="U16" s="9">
         <f t="shared" si="2"/>
-        <v>1.517241379310337E-2</v>
+        <v>7.5862068965516852E-3</v>
       </c>
       <c r="W16" s="1">
         <v>2861.9</v>
@@ -1925,22 +2144,22 @@
         <v>144</v>
       </c>
       <c r="Q17" s="1">
-        <v>145</v>
+        <v>143.69999999999999</v>
       </c>
       <c r="R17" s="1">
-        <v>145</v>
+        <v>143.69999999999999</v>
       </c>
       <c r="S17" s="1">
         <f t="shared" si="0"/>
-        <v>-15</v>
+        <v>-16.300000000000011</v>
       </c>
       <c r="T17" s="1">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>-0.30000000000001137</v>
       </c>
       <c r="U17" s="9">
         <f t="shared" si="2"/>
-        <v>6.9444444444444441E-3</v>
+        <v>-2.0833333333334122E-3</v>
       </c>
       <c r="W17" s="1">
         <v>2892.76</v>
@@ -1979,22 +2198,22 @@
         <v>11</v>
       </c>
       <c r="Q18" s="1">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="R18" s="1">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="S18" s="1">
         <f t="shared" si="0"/>
-        <v>0.40000000000000036</v>
+        <v>-9.9999999999999645E-2</v>
       </c>
       <c r="T18" s="1">
         <f t="shared" si="1"/>
-        <v>0.40000000000000036</v>
+        <v>-9.9999999999999645E-2</v>
       </c>
       <c r="U18" s="9">
         <f t="shared" si="2"/>
-        <v>3.6363636363636397E-2</v>
+        <v>-9.0909090909090592E-3</v>
       </c>
       <c r="W18" s="1">
         <v>80</v>
@@ -2091,22 +2310,22 @@
         <v>28</v>
       </c>
       <c r="Q20" s="1">
-        <v>27.2</v>
+        <v>27.9</v>
       </c>
       <c r="R20" s="1">
-        <v>27.2</v>
+        <v>27.9</v>
       </c>
       <c r="S20" s="1">
         <f t="shared" si="0"/>
-        <v>-0.80000000000000071</v>
+        <v>-0.10000000000000142</v>
       </c>
       <c r="T20" s="1">
         <f t="shared" si="1"/>
-        <v>-0.80000000000000071</v>
+        <v>-0.10000000000000142</v>
       </c>
       <c r="U20" s="9">
         <f t="shared" si="2"/>
-        <v>-2.8571428571428598E-2</v>
+        <v>-3.5714285714286221E-3</v>
       </c>
       <c r="W20" s="1">
         <v>400</v>
@@ -2147,22 +2366,22 @@
         <v>57</v>
       </c>
       <c r="Q21" s="1">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
       <c r="R21" s="1">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
       <c r="S21" s="1">
         <f t="shared" si="0"/>
-        <v>-0.20000000000000284</v>
+        <v>-0.29999999999999716</v>
       </c>
       <c r="T21" s="1">
         <f t="shared" si="1"/>
-        <v>-0.20000000000000284</v>
+        <v>-0.29999999999999716</v>
       </c>
       <c r="U21" s="9">
         <f t="shared" si="2"/>
-        <v>-3.5087719298246113E-3</v>
+        <v>-5.2631578947367925E-3</v>
       </c>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
@@ -2205,22 +2424,22 @@
         <v>112</v>
       </c>
       <c r="Q22" s="1">
-        <v>112.7</v>
+        <v>112.4</v>
       </c>
       <c r="R22" s="1">
-        <v>112.7</v>
+        <v>112.4</v>
       </c>
       <c r="S22" s="1">
         <f t="shared" si="0"/>
-        <v>0.70000000000000284</v>
+        <v>0.40000000000000568</v>
       </c>
       <c r="T22" s="1">
         <f t="shared" si="1"/>
-        <v>0.70000000000000284</v>
+        <v>0.40000000000000568</v>
       </c>
       <c r="U22" s="9">
         <f t="shared" si="2"/>
-        <v>6.2500000000000255E-3</v>
+        <v>3.5714285714286221E-3</v>
       </c>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
@@ -2263,22 +2482,22 @@
         <v>224</v>
       </c>
       <c r="Q23" s="1">
-        <v>224.3</v>
+        <v>224</v>
       </c>
       <c r="R23" s="1">
-        <v>224.3</v>
+        <v>224</v>
       </c>
       <c r="S23" s="1">
         <f t="shared" si="0"/>
-        <v>0.30000000000001137</v>
+        <v>0</v>
       </c>
       <c r="T23" s="1">
         <f t="shared" si="1"/>
-        <v>0.30000000000001137</v>
+        <v>0</v>
       </c>
       <c r="U23" s="9">
         <f t="shared" si="2"/>
-        <v>1.339285714285765E-3</v>
+        <v>0</v>
       </c>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
@@ -2321,22 +2540,22 @@
         <v>447</v>
       </c>
       <c r="Q24" s="1">
-        <v>447.8</v>
+        <v>447.4</v>
       </c>
       <c r="R24" s="1">
-        <v>447.8</v>
+        <v>447.4</v>
       </c>
       <c r="S24" s="1">
         <f t="shared" si="0"/>
-        <v>0.80000000000001137</v>
+        <v>0.39999999999997726</v>
       </c>
       <c r="T24" s="1">
         <f t="shared" si="1"/>
-        <v>0.80000000000001137</v>
+        <v>0.39999999999997726</v>
       </c>
       <c r="U24" s="9">
         <f t="shared" si="2"/>
-        <v>1.7897091722595332E-3</v>
+        <v>8.9485458612970309E-4</v>
       </c>
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
@@ -2379,22 +2598,22 @@
         <v>893</v>
       </c>
       <c r="Q25" s="1">
-        <v>894.9</v>
+        <v>894.1</v>
       </c>
       <c r="R25" s="1">
-        <v>894.9</v>
+        <v>894.1</v>
       </c>
       <c r="S25" s="1">
         <f t="shared" si="0"/>
-        <v>1.8999999999999773</v>
+        <v>1.1000000000000227</v>
       </c>
       <c r="T25" s="1">
         <f t="shared" si="1"/>
-        <v>1.8999999999999773</v>
+        <v>1.1000000000000227</v>
       </c>
       <c r="U25" s="9">
         <f t="shared" si="2"/>
-        <v>2.1276595744680596E-3</v>
+        <v>1.2318029115341799E-3</v>
       </c>
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
@@ -2437,22 +2656,22 @@
         <v>118</v>
       </c>
       <c r="Q26" s="1">
-        <v>118.4</v>
+        <v>118.1</v>
       </c>
       <c r="R26" s="1">
-        <v>118.4</v>
+        <v>118.1</v>
       </c>
       <c r="S26" s="1">
         <f t="shared" si="0"/>
-        <v>0.40000000000000568</v>
+        <v>9.9999999999994316E-2</v>
       </c>
       <c r="T26" s="1">
         <f t="shared" si="1"/>
-        <v>0.40000000000000568</v>
+        <v>9.9999999999994316E-2</v>
       </c>
       <c r="U26" s="9">
         <f t="shared" si="2"/>
-        <v>3.3898305084746243E-3</v>
+        <v>8.474576271185959E-4</v>
       </c>
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
@@ -2495,22 +2714,22 @@
         <v>158</v>
       </c>
       <c r="Q27" s="1">
-        <v>158.1</v>
+        <v>157.80000000000001</v>
       </c>
       <c r="R27" s="1">
-        <v>158.1</v>
+        <v>157.80000000000001</v>
       </c>
       <c r="S27" s="1">
         <f t="shared" si="0"/>
-        <v>9.9999999999994316E-2</v>
+        <v>-0.19999999999998863</v>
       </c>
       <c r="T27" s="1">
         <f t="shared" si="1"/>
-        <v>9.9999999999994316E-2</v>
+        <v>-0.19999999999998863</v>
       </c>
       <c r="U27" s="9">
         <f t="shared" si="2"/>
-        <v>6.3291139240502731E-4</v>
+        <v>-1.2658227848100546E-3</v>
       </c>
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
@@ -2553,22 +2772,22 @@
         <v>291</v>
       </c>
       <c r="Q28" s="1">
-        <v>290.5</v>
+        <v>290.2</v>
       </c>
       <c r="R28" s="1">
-        <v>290.5</v>
+        <v>290.2</v>
       </c>
       <c r="S28" s="1">
         <f t="shared" si="0"/>
-        <v>-0.5</v>
+        <v>-0.80000000000001137</v>
       </c>
       <c r="T28" s="1">
         <f t="shared" si="1"/>
-        <v>-0.5</v>
+        <v>-0.80000000000001137</v>
       </c>
       <c r="U28" s="9">
         <f t="shared" si="2"/>
-        <v>-1.718213058419244E-3</v>
+        <v>-2.7491408934708296E-3</v>
       </c>
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
@@ -2611,22 +2830,22 @@
         <v>357</v>
       </c>
       <c r="Q29" s="1">
-        <v>356.7</v>
+        <v>356.4</v>
       </c>
       <c r="R29" s="1">
-        <v>356.7</v>
+        <v>356.4</v>
       </c>
       <c r="S29" s="1">
         <f t="shared" si="0"/>
-        <v>-0.30000000000001137</v>
+        <v>-0.60000000000002274</v>
       </c>
       <c r="T29" s="1">
         <f t="shared" si="1"/>
-        <v>-0.30000000000001137</v>
+        <v>-0.60000000000002274</v>
       </c>
       <c r="U29" s="9">
         <f t="shared" si="2"/>
-        <v>-8.4033613445381333E-4</v>
+        <v>-1.6806722689076267E-3</v>
       </c>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
@@ -2669,22 +2888,22 @@
         <v>490</v>
       </c>
       <c r="Q30" s="1">
-        <v>489</v>
+        <v>488.7</v>
       </c>
       <c r="R30" s="1">
-        <v>489</v>
+        <v>488.7</v>
       </c>
       <c r="S30" s="1">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>-1.3000000000000114</v>
       </c>
       <c r="T30" s="1">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-1.3000000000000114</v>
       </c>
       <c r="U30" s="9">
         <f t="shared" si="2"/>
-        <v>-2.0408163265306124E-3</v>
+        <v>-2.6530612244898191E-3</v>
       </c>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
@@ -2727,22 +2946,22 @@
         <v>889</v>
       </c>
       <c r="Q31" s="1">
-        <v>890.7</v>
+        <v>890.1</v>
       </c>
       <c r="R31" s="1">
-        <v>890.7</v>
+        <v>890.1</v>
       </c>
       <c r="S31" s="1">
         <f t="shared" si="0"/>
-        <v>1.7000000000000455</v>
+        <v>1.1000000000000227</v>
       </c>
       <c r="T31" s="1">
         <f t="shared" si="1"/>
-        <v>1.7000000000000455</v>
+        <v>1.1000000000000227</v>
       </c>
       <c r="U31" s="9">
         <f t="shared" si="2"/>
-        <v>1.9122609673791287E-3</v>
+        <v>1.2373453318335465E-3</v>
       </c>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
@@ -2785,22 +3004,22 @@
         <v>534</v>
       </c>
       <c r="Q32" s="1">
-        <v>534.79999999999995</v>
+        <v>534.4</v>
       </c>
       <c r="R32" s="1">
-        <v>534.79999999999995</v>
+        <v>534.4</v>
       </c>
       <c r="S32" s="1">
         <f t="shared" si="0"/>
-        <v>0.79999999999995453</v>
+        <v>0.39999999999997726</v>
       </c>
       <c r="T32" s="1">
         <f t="shared" si="1"/>
-        <v>0.79999999999995453</v>
+        <v>0.39999999999997726</v>
       </c>
       <c r="U32" s="9">
         <f t="shared" si="2"/>
-        <v>1.4981273408238849E-3</v>
+        <v>7.4906367041194244E-4</v>
       </c>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
@@ -2843,22 +3062,22 @@
         <v>559</v>
       </c>
       <c r="Q33" s="1">
-        <v>559.79999999999995</v>
+        <v>559.20000000000005</v>
       </c>
       <c r="R33" s="1">
-        <v>559.79999999999995</v>
+        <v>559.20000000000005</v>
       </c>
       <c r="S33" s="1">
         <f t="shared" si="0"/>
-        <v>0.79999999999995453</v>
+        <v>0.20000000000004547</v>
       </c>
       <c r="T33" s="1">
         <f t="shared" si="1"/>
-        <v>0.79999999999995453</v>
+        <v>0.20000000000004547</v>
       </c>
       <c r="U33" s="9">
         <f t="shared" si="2"/>
-        <v>1.43112701252228E-3</v>
+        <v>3.577817531306717E-4</v>
       </c>
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
@@ -2901,22 +3120,22 @@
         <v>606</v>
       </c>
       <c r="Q34" s="1">
-        <v>606.70000000000005</v>
+        <v>606.20000000000005</v>
       </c>
       <c r="R34" s="1">
-        <v>606.70000000000005</v>
+        <v>606.20000000000005</v>
       </c>
       <c r="S34" s="1">
         <f t="shared" si="0"/>
-        <v>0.70000000000004547</v>
+        <v>0.20000000000004547</v>
       </c>
       <c r="T34" s="1">
         <f t="shared" si="1"/>
-        <v>0.70000000000004547</v>
+        <v>0.20000000000004547</v>
       </c>
       <c r="U34" s="9">
         <f t="shared" si="2"/>
-        <v>1.1551155115512302E-3</v>
+        <v>3.3003300330040506E-4</v>
       </c>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
@@ -2959,22 +3178,22 @@
         <v>126</v>
       </c>
       <c r="Q35" s="1">
-        <v>127.1</v>
+        <v>125.6</v>
       </c>
       <c r="R35" s="1">
-        <v>126.9</v>
+        <v>125.6</v>
       </c>
       <c r="S35" s="1">
         <f t="shared" si="0"/>
-        <v>1.0999999999999943</v>
+        <v>-0.40000000000000568</v>
       </c>
       <c r="T35" s="1">
         <f t="shared" si="1"/>
-        <v>0.90000000000000568</v>
+        <v>-0.40000000000000568</v>
       </c>
       <c r="U35" s="9">
         <f t="shared" si="2"/>
-        <v>7.1428571428571877E-3</v>
+        <v>-3.1746031746032197E-3</v>
       </c>
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
@@ -3011,22 +3230,22 @@
         <v>121</v>
       </c>
       <c r="Q36" s="1">
-        <v>122.2</v>
+        <v>119.9</v>
       </c>
       <c r="R36" s="1">
-        <v>122.2</v>
+        <v>119.9</v>
       </c>
       <c r="S36" s="1">
         <f t="shared" si="0"/>
-        <v>1.2000000000000028</v>
+        <v>-1.0999999999999943</v>
       </c>
       <c r="T36" s="1">
         <f t="shared" si="1"/>
-        <v>1.2000000000000028</v>
+        <v>-1.0999999999999943</v>
       </c>
       <c r="U36" s="9">
         <f t="shared" si="2"/>
-        <v>9.9173553719008496E-3</v>
+        <v>-9.0909090909090436E-3</v>
       </c>
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
@@ -3063,22 +3282,22 @@
         <v>54</v>
       </c>
       <c r="Q37" s="1">
-        <v>54.2</v>
+        <v>53.7</v>
       </c>
       <c r="R37" s="1">
-        <v>54.2</v>
+        <v>53.7</v>
       </c>
       <c r="S37" s="1">
         <f t="shared" si="0"/>
-        <v>0.20000000000000284</v>
+        <v>-0.29999999999999716</v>
       </c>
       <c r="T37" s="1">
         <f t="shared" si="1"/>
-        <v>0.20000000000000284</v>
+        <v>-0.29999999999999716</v>
       </c>
       <c r="U37" s="9">
         <f t="shared" si="2"/>
-        <v>3.7037037037037563E-3</v>
+        <v>-5.5555555555555029E-3</v>
       </c>
       <c r="W37" s="1">
         <v>2000</v>
@@ -3119,22 +3338,22 @@
         <v>28</v>
       </c>
       <c r="Q38" s="1">
-        <v>28.1</v>
+        <v>27.8</v>
       </c>
       <c r="R38" s="1">
-        <v>28.1</v>
+        <v>27.8</v>
       </c>
       <c r="S38" s="1">
         <f t="shared" si="0"/>
-        <v>0.10000000000000142</v>
+        <v>-0.19999999999999929</v>
       </c>
       <c r="T38" s="1">
         <f t="shared" si="1"/>
-        <v>0.10000000000000142</v>
+        <v>-0.19999999999999929</v>
       </c>
       <c r="U38" s="9">
         <f t="shared" si="2"/>
-        <v>3.5714285714286221E-3</v>
+        <v>-7.1428571428571175E-3</v>
       </c>
       <c r="W38" s="1">
         <v>2000</v>
@@ -3175,22 +3394,22 @@
         <v>18</v>
       </c>
       <c r="Q39" s="1">
-        <v>17.899999999999999</v>
+        <v>17.7</v>
       </c>
       <c r="R39" s="1">
-        <v>17.899999999999999</v>
+        <v>17.7</v>
       </c>
       <c r="S39" s="1">
         <f t="shared" si="0"/>
-        <v>-0.10000000000000142</v>
+        <v>-0.30000000000000071</v>
       </c>
       <c r="T39" s="1">
         <f t="shared" si="1"/>
-        <v>-0.10000000000000142</v>
+        <v>-0.30000000000000071</v>
       </c>
       <c r="U39" s="9">
         <f t="shared" si="2"/>
-        <v>-5.5555555555556347E-3</v>
+        <v>-1.6666666666666705E-2</v>
       </c>
       <c r="W39" s="1">
         <v>2000</v>
@@ -3231,22 +3450,22 @@
         <v>13</v>
       </c>
       <c r="Q40" s="1">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="R40" s="1">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="S40" s="1">
         <f t="shared" si="0"/>
-        <v>0.19999999999999929</v>
+        <v>0</v>
       </c>
       <c r="T40" s="1">
         <f t="shared" si="1"/>
-        <v>0.19999999999999929</v>
+        <v>0</v>
       </c>
       <c r="U40" s="9">
         <f t="shared" si="2"/>
-        <v>1.538461538461533E-2</v>
+        <v>0</v>
       </c>
       <c r="W40" s="1">
         <v>2000</v>
@@ -3287,22 +3506,22 @@
         <v>11</v>
       </c>
       <c r="Q41" s="1">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="R41" s="1">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="S41" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-0.19999999999999929</v>
       </c>
       <c r="T41" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-0.19999999999999929</v>
       </c>
       <c r="U41" s="9">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1.8181818181818118E-2</v>
       </c>
       <c r="W41" s="1">
         <v>2000</v>
@@ -3343,22 +3562,22 @@
         <v>33</v>
       </c>
       <c r="Q42" s="1">
-        <v>32.700000000000003</v>
+        <v>32</v>
       </c>
       <c r="R42" s="1">
-        <v>32.700000000000003</v>
+        <v>32</v>
       </c>
       <c r="S42" s="1">
         <f t="shared" si="0"/>
-        <v>0.70000000000000284</v>
+        <v>0</v>
       </c>
       <c r="T42" s="1">
         <f t="shared" si="1"/>
-        <v>-0.29999999999999716</v>
+        <v>-1</v>
       </c>
       <c r="U42" s="9">
         <f t="shared" si="2"/>
-        <v>-9.0909090909090055E-3</v>
+        <v>-3.0303030303030304E-2</v>
       </c>
       <c r="W42" s="1">
         <v>1565.44</v>
@@ -3399,22 +3618,22 @@
         <v>312</v>
       </c>
       <c r="Q43" s="1">
-        <v>312.39999999999998</v>
+        <v>315.10000000000002</v>
       </c>
       <c r="R43" s="1">
-        <v>312.39999999999998</v>
+        <v>315.10000000000002</v>
       </c>
       <c r="S43" s="1">
         <f t="shared" si="0"/>
-        <v>0.39999999999997726</v>
+        <v>3.1000000000000227</v>
       </c>
       <c r="T43" s="1">
         <f t="shared" si="1"/>
-        <v>0.39999999999997726</v>
+        <v>3.1000000000000227</v>
       </c>
       <c r="U43" s="9">
         <f t="shared" si="2"/>
-        <v>1.2820512820512092E-3</v>
+        <v>9.9358974358975082E-3</v>
       </c>
       <c r="W43" s="1"/>
       <c r="X43" s="1"/>
@@ -3457,22 +3676,22 @@
         <v>1192</v>
       </c>
       <c r="Q44" s="1">
-        <v>1195.2</v>
+        <v>1188.4000000000001</v>
       </c>
       <c r="R44" s="1">
-        <v>1195.2</v>
+        <v>1188.4000000000001</v>
       </c>
       <c r="S44" s="1">
         <f t="shared" si="0"/>
-        <v>3.2000000000000455</v>
+        <v>-3.5999999999999091</v>
       </c>
       <c r="T44" s="1">
         <f t="shared" si="1"/>
-        <v>3.2000000000000455</v>
+        <v>-3.5999999999999091</v>
       </c>
       <c r="U44" s="9">
         <f t="shared" si="2"/>
-        <v>2.6845637583892998E-3</v>
+        <v>-3.020134228187843E-3</v>
       </c>
       <c r="W44" s="1"/>
       <c r="X44" s="1"/>
@@ -3515,22 +3734,22 @@
         <v>1156</v>
       </c>
       <c r="Q45" s="1">
-        <v>1152.5999999999999</v>
+        <v>1153.3</v>
       </c>
       <c r="R45" s="1">
-        <v>1152.5999999999999</v>
+        <v>1153.3</v>
       </c>
       <c r="S45" s="1">
         <f t="shared" si="0"/>
-        <v>-3.4000000000000909</v>
+        <v>-2.7000000000000455</v>
       </c>
       <c r="T45" s="1">
         <f t="shared" si="1"/>
-        <v>-3.4000000000000909</v>
+        <v>-2.7000000000000455</v>
       </c>
       <c r="U45" s="9">
         <f t="shared" si="2"/>
-        <v>-2.9411764705883142E-3</v>
+        <v>-2.3356401384083438E-3</v>
       </c>
       <c r="W45" s="1"/>
       <c r="X45" s="1"/>
@@ -3573,22 +3792,22 @@
         <v>391</v>
       </c>
       <c r="Q46" s="1">
-        <v>391.1</v>
+        <v>387.7</v>
       </c>
       <c r="R46" s="1">
-        <v>391.1</v>
+        <v>387.7</v>
       </c>
       <c r="S46" s="1">
         <f t="shared" si="0"/>
-        <v>0.10000000000002274</v>
+        <v>-3.3000000000000114</v>
       </c>
       <c r="T46" s="1">
         <f t="shared" si="1"/>
-        <v>0.10000000000002274</v>
+        <v>-3.3000000000000114</v>
       </c>
       <c r="U46" s="9">
         <f t="shared" si="2"/>
-        <v>2.5575447570338295E-4</v>
+        <v>-8.439897698209747E-3</v>
       </c>
       <c r="W46" s="1"/>
       <c r="X46" s="1"/>
@@ -3631,22 +3850,22 @@
         <v>204</v>
       </c>
       <c r="Q47" s="1">
-        <v>204.6</v>
+        <v>205.8</v>
       </c>
       <c r="R47" s="1">
-        <v>204.6</v>
+        <v>205.8</v>
       </c>
       <c r="S47" s="1">
         <f t="shared" si="0"/>
-        <v>0.59999999999999432</v>
+        <v>1.8000000000000114</v>
       </c>
       <c r="T47" s="1">
         <f t="shared" si="1"/>
-        <v>0.59999999999999432</v>
+        <v>1.8000000000000114</v>
       </c>
       <c r="U47" s="9">
         <f t="shared" si="2"/>
-        <v>2.9411764705882075E-3</v>
+        <v>8.8235294117647613E-3</v>
       </c>
       <c r="W47" s="1"/>
       <c r="X47" s="1"/>
@@ -3689,22 +3908,22 @@
         <v>2288</v>
       </c>
       <c r="Q48" s="1">
-        <v>2286.9</v>
+        <v>2282.4</v>
       </c>
       <c r="R48" s="1">
-        <v>2286.9</v>
+        <v>2282.4</v>
       </c>
       <c r="S48" s="1">
         <f t="shared" si="0"/>
-        <v>-1.0999999999999091</v>
+        <v>-5.5999999999999091</v>
       </c>
       <c r="T48" s="1">
         <f t="shared" si="1"/>
-        <v>-1.0999999999999091</v>
+        <v>-5.5999999999999091</v>
       </c>
       <c r="U48" s="9">
         <f t="shared" si="2"/>
-        <v>-4.8076923076919101E-4</v>
+        <v>-2.4475524475524079E-3</v>
       </c>
       <c r="W48" s="1"/>
       <c r="X48" s="1"/>
@@ -3740,27 +3959,31 @@
         <v>0</v>
       </c>
       <c r="E51" s="1"/>
-      <c r="G51" s="1"/>
+      <c r="G51">
+        <v>341</v>
+      </c>
       <c r="H51" s="1"/>
-      <c r="I51" s="6"/>
+      <c r="I51">
+        <v>341</v>
+      </c>
       <c r="J51" s="6"/>
       <c r="Q51" s="1">
-        <v>320.89999999999998</v>
+        <v>341</v>
       </c>
       <c r="R51" s="1">
-        <v>320.89999999999998</v>
-      </c>
-      <c r="S51" s="1" t="str">
+        <v>341</v>
+      </c>
+      <c r="S51" s="1">
         <f t="shared" ref="S51:S73" si="3">IF(AND(ISNUMBER(Q51),ISNUMBER(G51)),Q51-G51,"")</f>
-        <v/>
-      </c>
-      <c r="T51" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="T51" s="1">
         <f t="shared" ref="T51:T73" si="4">IF(AND(ISNUMBER(R51),ISNUMBER(I51)),R51-I51,"")</f>
-        <v/>
-      </c>
-      <c r="U51" s="9" t="str">
+        <v>0</v>
+      </c>
+      <c r="U51" s="9">
         <f t="shared" ref="U51:U73" si="5">IF(AND(ISNUMBER(R51),ISNUMBER(I51),I51&lt;&gt;0),(R51-I51)/I51,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W51" s="1"/>
       <c r="X51" s="1"/>
@@ -3788,27 +4011,31 @@
         <v>0</v>
       </c>
       <c r="E52" s="1"/>
-      <c r="G52" s="1"/>
+      <c r="G52" s="1">
+        <v>334</v>
+      </c>
       <c r="H52" s="1"/>
-      <c r="I52" s="6"/>
+      <c r="I52" s="6">
+        <v>334</v>
+      </c>
       <c r="J52" s="6"/>
       <c r="Q52" s="1">
-        <v>286.2</v>
+        <v>334</v>
       </c>
       <c r="R52" s="1">
-        <v>286.2</v>
-      </c>
-      <c r="S52" s="1" t="str">
+        <v>334</v>
+      </c>
+      <c r="S52" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T52" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="T52" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U52" s="9" t="str">
+        <v>0</v>
+      </c>
+      <c r="U52" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W52" s="1"/>
       <c r="X52" s="1"/>
@@ -3836,27 +4063,33 @@
         <v>0</v>
       </c>
       <c r="E53" s="1"/>
-      <c r="G53" s="1"/>
+      <c r="G53" s="1">
+        <v>300</v>
+      </c>
       <c r="H53" s="1"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
+      <c r="I53" s="6">
+        <v>300</v>
+      </c>
+      <c r="J53" s="6">
+        <v>300</v>
+      </c>
       <c r="Q53" s="1">
-        <v>265.5</v>
+        <v>302.5</v>
       </c>
       <c r="R53" s="1">
-        <v>265.5</v>
-      </c>
-      <c r="S53" s="1" t="str">
+        <v>302.5</v>
+      </c>
+      <c r="S53" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T53" s="1" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="T53" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U53" s="9" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="U53" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>8.3333333333333332E-3</v>
       </c>
       <c r="W53" s="1"/>
       <c r="X53" s="1"/>
@@ -3884,27 +4117,31 @@
         <v>0</v>
       </c>
       <c r="E54" s="1"/>
-      <c r="G54" s="1"/>
+      <c r="G54" s="1">
+        <v>117</v>
+      </c>
       <c r="H54" s="1"/>
-      <c r="I54" s="6"/>
+      <c r="I54" s="6">
+        <v>117</v>
+      </c>
       <c r="J54" s="6"/>
       <c r="Q54" s="1">
-        <v>117</v>
+        <v>118.3</v>
       </c>
       <c r="R54" s="1">
-        <v>117</v>
-      </c>
-      <c r="S54" s="1" t="str">
+        <v>118.3</v>
+      </c>
+      <c r="S54" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T54" s="1" t="str">
+        <v>1.2999999999999972</v>
+      </c>
+      <c r="T54" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U54" s="9" t="str">
+        <v>1.2999999999999972</v>
+      </c>
+      <c r="U54" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1.1111111111111087E-2</v>
       </c>
       <c r="W54" s="1"/>
       <c r="X54" s="1"/>
@@ -3932,27 +4169,31 @@
         <v>0</v>
       </c>
       <c r="E55" s="1"/>
-      <c r="G55" s="1"/>
+      <c r="G55" s="1">
+        <v>436</v>
+      </c>
       <c r="H55" s="1"/>
-      <c r="I55" s="6"/>
+      <c r="I55" s="1">
+        <v>436</v>
+      </c>
       <c r="J55" s="6"/>
       <c r="Q55" s="1">
-        <v>439.2</v>
+        <v>435.7</v>
       </c>
       <c r="R55" s="1">
-        <v>439.2</v>
-      </c>
-      <c r="S55" s="1" t="str">
+        <v>435.7</v>
+      </c>
+      <c r="S55" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T55" s="1" t="str">
+        <v>-0.30000000000001137</v>
+      </c>
+      <c r="T55" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U55" s="9" t="str">
+        <v>-0.30000000000001137</v>
+      </c>
+      <c r="U55" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>-6.880733944954389E-4</v>
       </c>
       <c r="W55" s="1"/>
       <c r="X55" s="1"/>
@@ -3980,27 +4221,31 @@
         <v>0</v>
       </c>
       <c r="E56" s="1"/>
-      <c r="G56" s="1"/>
+      <c r="G56" s="1">
+        <v>97</v>
+      </c>
       <c r="H56" s="1"/>
-      <c r="I56" s="6"/>
+      <c r="I56" s="6">
+        <v>84</v>
+      </c>
       <c r="J56" s="6"/>
       <c r="Q56" s="1">
-        <v>96.2</v>
+        <v>98.2</v>
       </c>
       <c r="R56" s="1">
-        <v>82.4</v>
-      </c>
-      <c r="S56" s="1" t="str">
+        <v>84.4</v>
+      </c>
+      <c r="S56" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T56" s="1" t="str">
+        <v>1.2000000000000028</v>
+      </c>
+      <c r="T56" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U56" s="9" t="str">
+        <v>0.40000000000000568</v>
+      </c>
+      <c r="U56" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>4.76190476190483E-3</v>
       </c>
       <c r="W56" s="1">
         <v>1200</v>
@@ -4032,27 +4277,31 @@
         <v>0</v>
       </c>
       <c r="E57" s="1"/>
-      <c r="G57" s="1"/>
+      <c r="G57" s="1">
+        <v>131</v>
+      </c>
       <c r="H57" s="1"/>
-      <c r="I57" s="6"/>
+      <c r="I57" s="6">
+        <v>84</v>
+      </c>
       <c r="J57" s="6"/>
       <c r="Q57" s="1">
         <v>133</v>
       </c>
       <c r="R57" s="1">
-        <v>82.4</v>
-      </c>
-      <c r="S57" s="1" t="str">
+        <v>84.4</v>
+      </c>
+      <c r="S57" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T57" s="1" t="str">
+        <v>2</v>
+      </c>
+      <c r="T57" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U57" s="9" t="str">
+        <v>0.40000000000000568</v>
+      </c>
+      <c r="U57" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>4.76190476190483E-3</v>
       </c>
       <c r="W57" s="1">
         <v>1200</v>
@@ -4084,27 +4333,31 @@
         <v>0</v>
       </c>
       <c r="E58" s="1"/>
-      <c r="G58" s="1"/>
+      <c r="G58" s="1">
+        <v>94</v>
+      </c>
       <c r="H58" s="1"/>
-      <c r="I58" s="6"/>
+      <c r="I58" s="6">
+        <v>55</v>
+      </c>
       <c r="J58" s="6"/>
       <c r="Q58" s="1">
         <v>95.7</v>
       </c>
       <c r="R58" s="1">
-        <v>50.9</v>
-      </c>
-      <c r="S58" s="1" t="str">
+        <v>55.8</v>
+      </c>
+      <c r="S58" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T58" s="1" t="str">
+        <v>1.7000000000000028</v>
+      </c>
+      <c r="T58" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U58" s="9" t="str">
+        <v>0.79999999999999716</v>
+      </c>
+      <c r="U58" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1.4545454545454493E-2</v>
       </c>
       <c r="W58" s="1">
         <v>480</v>
@@ -4138,27 +4391,31 @@
         <v>0</v>
       </c>
       <c r="E59" s="1"/>
-      <c r="G59" s="1"/>
+      <c r="G59" s="1">
+        <v>122</v>
+      </c>
       <c r="H59" s="1"/>
-      <c r="I59" s="6"/>
+      <c r="I59" s="6">
+        <v>123</v>
+      </c>
       <c r="J59" s="6"/>
       <c r="Q59" s="1">
-        <v>127.7</v>
+        <v>123</v>
       </c>
       <c r="R59" s="1">
-        <v>127.7</v>
-      </c>
-      <c r="S59" s="1" t="str">
+        <v>123</v>
+      </c>
+      <c r="S59" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T59" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="T59" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U59" s="9" t="str">
+        <v>0</v>
+      </c>
+      <c r="U59" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W59" s="1">
         <v>2000</v>
@@ -4192,27 +4449,31 @@
         <v>0</v>
       </c>
       <c r="E60" s="1"/>
-      <c r="G60" s="1"/>
+      <c r="G60" s="1">
+        <v>131</v>
+      </c>
       <c r="H60" s="1"/>
-      <c r="I60" s="6"/>
+      <c r="I60" s="6">
+        <v>132</v>
+      </c>
       <c r="J60" s="6"/>
       <c r="Q60" s="1">
-        <v>136.5</v>
+        <v>131.9</v>
       </c>
       <c r="R60" s="1">
-        <v>136.5</v>
-      </c>
-      <c r="S60" s="1" t="str">
+        <v>131.9</v>
+      </c>
+      <c r="S60" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T60" s="1" t="str">
+        <v>0.90000000000000568</v>
+      </c>
+      <c r="T60" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U60" s="9" t="str">
+        <v>-9.9999999999994316E-2</v>
+      </c>
+      <c r="U60" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>-7.5757575757571453E-4</v>
       </c>
       <c r="W60" s="1">
         <v>2000</v>
@@ -4246,27 +4507,31 @@
         <v>0</v>
       </c>
       <c r="E61" s="1"/>
-      <c r="G61" s="1"/>
+      <c r="G61" s="1">
+        <v>146</v>
+      </c>
       <c r="H61" s="1"/>
-      <c r="I61" s="6"/>
+      <c r="I61" s="1">
+        <v>146</v>
+      </c>
       <c r="J61" s="6"/>
       <c r="Q61" s="1">
-        <v>150.4</v>
+        <v>147</v>
       </c>
       <c r="R61" s="1">
-        <v>150.4</v>
-      </c>
-      <c r="S61" s="1" t="str">
+        <v>147</v>
+      </c>
+      <c r="S61" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T61" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="T61" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U61" s="9" t="str">
+        <v>1</v>
+      </c>
+      <c r="U61" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>6.8493150684931503E-3</v>
       </c>
       <c r="W61" s="1">
         <v>2000</v>
@@ -4300,27 +4565,31 @@
         <v>0</v>
       </c>
       <c r="E62" s="1"/>
-      <c r="G62" s="1"/>
+      <c r="G62" s="1">
+        <v>5</v>
+      </c>
       <c r="H62" s="1"/>
-      <c r="I62" s="6"/>
+      <c r="I62" s="6">
+        <v>5</v>
+      </c>
       <c r="J62" s="6"/>
       <c r="Q62" s="1">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="R62" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="S62" s="1" t="str">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="S62" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T62" s="1" t="str">
+        <v>-9.9999999999999645E-2</v>
+      </c>
+      <c r="T62" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U62" s="9" t="str">
+        <v>-9.9999999999999645E-2</v>
+      </c>
+      <c r="U62" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>-1.9999999999999928E-2</v>
       </c>
       <c r="W62" s="1">
         <v>80</v>
@@ -4352,27 +4621,31 @@
         <v>0</v>
       </c>
       <c r="E63" s="1"/>
-      <c r="G63" s="1"/>
+      <c r="G63" s="1">
+        <v>13</v>
+      </c>
       <c r="H63" s="1"/>
-      <c r="I63" s="6"/>
+      <c r="I63" s="6">
+        <v>13</v>
+      </c>
       <c r="J63" s="6"/>
       <c r="Q63" s="1">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="R63" s="1">
-        <v>9.4</v>
-      </c>
-      <c r="S63" s="1" t="str">
+        <v>13.5</v>
+      </c>
+      <c r="S63" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T63" s="1" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="T63" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U63" s="9" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="U63" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>3.8461538461538464E-2</v>
       </c>
       <c r="W63" s="1">
         <v>80</v>
@@ -4406,27 +4679,31 @@
         <v>0</v>
       </c>
       <c r="E64" s="1"/>
-      <c r="G64" s="1"/>
+      <c r="G64" s="1">
+        <v>28</v>
+      </c>
       <c r="H64" s="1"/>
-      <c r="I64" s="6"/>
+      <c r="I64" s="6">
+        <v>25</v>
+      </c>
       <c r="J64" s="6"/>
       <c r="Q64" s="1">
-        <v>34.799999999999997</v>
+        <v>27.7</v>
       </c>
       <c r="R64" s="1">
-        <v>32</v>
-      </c>
-      <c r="S64" s="1" t="str">
+        <v>25</v>
+      </c>
+      <c r="S64" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T64" s="1" t="str">
+        <v>-0.30000000000000071</v>
+      </c>
+      <c r="T64" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U64" s="9" t="str">
+        <v>0</v>
+      </c>
+      <c r="U64" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W64" s="1">
         <v>200</v>
@@ -4460,27 +4737,31 @@
         <v>0</v>
       </c>
       <c r="E65" s="1"/>
-      <c r="G65" s="1"/>
+      <c r="G65" s="1">
+        <v>153</v>
+      </c>
       <c r="H65" s="1"/>
-      <c r="I65" s="6"/>
+      <c r="I65" s="6">
+        <v>139</v>
+      </c>
       <c r="J65" s="6"/>
       <c r="Q65" s="1">
-        <v>135.6</v>
+        <v>137.6</v>
       </c>
       <c r="R65" s="1">
-        <v>135.6</v>
-      </c>
-      <c r="S65" s="1" t="str">
+        <v>137.6</v>
+      </c>
+      <c r="S65" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T65" s="1" t="str">
+        <v>-15.400000000000006</v>
+      </c>
+      <c r="T65" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U65" s="9" t="str">
+        <v>-1.4000000000000057</v>
+      </c>
+      <c r="U65" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>-1.0071942446043206E-2</v>
       </c>
       <c r="W65" s="1">
         <v>2700</v>
@@ -4514,27 +4795,31 @@
         <v>0</v>
       </c>
       <c r="E66" s="1"/>
-      <c r="G66" s="1"/>
+      <c r="G66" s="1">
+        <v>153</v>
+      </c>
       <c r="H66" s="1"/>
-      <c r="I66" s="6"/>
+      <c r="I66" s="6">
+        <v>139</v>
+      </c>
       <c r="J66" s="6"/>
       <c r="Q66" s="1">
-        <v>135.6</v>
+        <v>137.69999999999999</v>
       </c>
       <c r="R66" s="1">
-        <v>135.6</v>
-      </c>
-      <c r="S66" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T66" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U66" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v/>
+        <v>137.69999999999999</v>
+      </c>
+      <c r="S66" s="1">
+        <f>IF(AND(ISNUMBER(Q66),ISNUMBER(G67)),Q66-G67,"")</f>
+        <v>-15.300000000000011</v>
+      </c>
+      <c r="T66" s="1">
+        <f>IF(AND(ISNUMBER(R66),ISNUMBER(I67)),R66-I67,"")</f>
+        <v>-1.3000000000000114</v>
+      </c>
+      <c r="U66" s="9">
+        <f>IF(AND(ISNUMBER(R66),ISNUMBER(I67),I67&lt;&gt;0),(R66-I67)/I67,"")</f>
+        <v>-9.3525179856115918E-3</v>
       </c>
       <c r="W66" s="1">
         <v>2700</v>
@@ -4568,27 +4853,31 @@
         <v>0</v>
       </c>
       <c r="E67" s="1"/>
-      <c r="G67" s="1"/>
+      <c r="G67" s="1">
+        <v>153</v>
+      </c>
       <c r="H67" s="1"/>
-      <c r="I67" s="6"/>
+      <c r="I67" s="6">
+        <v>139</v>
+      </c>
       <c r="J67" s="6"/>
       <c r="Q67" s="1">
-        <v>140.69999999999999</v>
+        <v>137.69999999999999</v>
       </c>
       <c r="R67" s="1">
-        <v>140.69999999999999</v>
-      </c>
-      <c r="S67" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T67" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U67" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v/>
+        <v>137.69999999999999</v>
+      </c>
+      <c r="S67" s="1">
+        <f>IF(AND(ISNUMBER(Q67),ISNUMBER(G68)),Q67-G68,"")</f>
+        <v>-15.300000000000011</v>
+      </c>
+      <c r="T67" s="1">
+        <f>IF(AND(ISNUMBER(R67),ISNUMBER(I68)),R67-I68,"")</f>
+        <v>-0.30000000000001137</v>
+      </c>
+      <c r="U67" s="9">
+        <f>IF(AND(ISNUMBER(R67),ISNUMBER(I68),I68&lt;&gt;0),(R67-I68)/I68,"")</f>
+        <v>-2.1739130434783433E-3</v>
       </c>
       <c r="W67" s="1">
         <v>2700</v>
@@ -4622,27 +4911,35 @@
         <v>0</v>
       </c>
       <c r="E68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="6"/>
-      <c r="J68" s="6"/>
+      <c r="G68" s="1">
+        <v>153</v>
+      </c>
+      <c r="H68" s="1">
+        <v>160</v>
+      </c>
+      <c r="I68" s="6">
+        <v>138</v>
+      </c>
+      <c r="J68" s="6">
+        <v>137</v>
+      </c>
       <c r="Q68" s="1">
-        <v>150.9</v>
+        <v>137.69999999999999</v>
       </c>
       <c r="R68" s="1">
-        <v>150.9</v>
-      </c>
-      <c r="S68" s="1" t="str">
+        <v>137.69999999999999</v>
+      </c>
+      <c r="S68" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T68" s="1" t="str">
+        <v>-15.300000000000011</v>
+      </c>
+      <c r="T68" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U68" s="9" t="str">
+        <v>-0.30000000000001137</v>
+      </c>
+      <c r="U68" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>-2.1739130434783433E-3</v>
       </c>
       <c r="W68" s="1">
         <v>2700</v>
@@ -4676,27 +4973,31 @@
         <v>0</v>
       </c>
       <c r="E69" s="1"/>
-      <c r="G69" s="1"/>
+      <c r="G69" s="1">
+        <v>153</v>
+      </c>
       <c r="H69" s="1"/>
-      <c r="I69" s="6"/>
+      <c r="I69" s="6">
+        <v>154</v>
+      </c>
       <c r="J69" s="6"/>
       <c r="Q69" s="1">
-        <v>150.9</v>
+        <v>153.6</v>
       </c>
       <c r="R69" s="1">
-        <v>150.9</v>
-      </c>
-      <c r="S69" s="1" t="str">
+        <v>153.6</v>
+      </c>
+      <c r="S69" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T69" s="1" t="str">
+        <v>0.59999999999999432</v>
+      </c>
+      <c r="T69" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U69" s="9" t="str">
+        <v>-0.40000000000000568</v>
+      </c>
+      <c r="U69" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>-2.5974025974026343E-3</v>
       </c>
       <c r="W69" s="1">
         <v>2700</v>
@@ -4730,27 +5031,31 @@
         <v>0</v>
       </c>
       <c r="E70" s="1"/>
-      <c r="G70" s="1"/>
+      <c r="G70" s="1">
+        <v>74</v>
+      </c>
       <c r="H70" s="1"/>
-      <c r="I70" s="6"/>
+      <c r="I70" s="6">
+        <v>74</v>
+      </c>
       <c r="J70" s="6"/>
       <c r="Q70" s="1">
-        <v>71.599999999999994</v>
+        <v>74.2</v>
       </c>
       <c r="R70" s="1">
-        <v>71.599999999999994</v>
-      </c>
-      <c r="S70" s="1" t="str">
+        <v>74.2</v>
+      </c>
+      <c r="S70" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T70" s="1" t="str">
+        <v>0.20000000000000284</v>
+      </c>
+      <c r="T70" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U70" s="9" t="str">
+        <v>0.20000000000000284</v>
+      </c>
+      <c r="U70" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>2.702702702702741E-3</v>
       </c>
       <c r="W70" s="1">
         <v>1338.3</v>
@@ -4784,27 +5089,31 @@
         <v>0</v>
       </c>
       <c r="E71" s="1"/>
-      <c r="G71" s="1"/>
+      <c r="G71" s="1">
+        <v>94</v>
+      </c>
       <c r="H71" s="1"/>
-      <c r="I71" s="6"/>
+      <c r="I71" s="6">
+        <v>74</v>
+      </c>
       <c r="J71" s="6"/>
       <c r="Q71" s="1">
-        <v>71.599999999999994</v>
+        <v>74.2</v>
       </c>
       <c r="R71" s="1">
-        <v>71.599999999999994</v>
-      </c>
-      <c r="S71" s="1" t="str">
+        <v>74.2</v>
+      </c>
+      <c r="S71" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T71" s="1" t="str">
+        <v>-19.799999999999997</v>
+      </c>
+      <c r="T71" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U71" s="9" t="str">
+        <v>0.20000000000000284</v>
+      </c>
+      <c r="U71" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>2.702702702702741E-3</v>
       </c>
       <c r="W71" s="1">
         <v>1338.3</v>
@@ -4838,27 +5147,31 @@
         <v>0</v>
       </c>
       <c r="E72" s="1"/>
-      <c r="G72" s="1"/>
+      <c r="G72" s="1">
+        <v>379</v>
+      </c>
       <c r="H72" s="1"/>
-      <c r="I72" s="6"/>
+      <c r="I72" s="1">
+        <v>379</v>
+      </c>
       <c r="J72" s="6"/>
       <c r="Q72" s="1">
-        <v>380.4</v>
+        <v>379.3</v>
       </c>
       <c r="R72" s="1">
-        <v>380.4</v>
-      </c>
-      <c r="S72" s="1" t="str">
+        <v>379.3</v>
+      </c>
+      <c r="S72" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T72" s="1" t="str">
+        <v>0.30000000000001137</v>
+      </c>
+      <c r="T72" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U72" s="9" t="str">
+        <v>0.30000000000001137</v>
+      </c>
+      <c r="U72" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>7.9155672823221998E-4</v>
       </c>
       <c r="W72" s="1">
         <v>0</v>
@@ -4892,27 +5205,31 @@
         <v>0</v>
       </c>
       <c r="E73" s="1"/>
-      <c r="G73" s="1"/>
+      <c r="G73" s="1">
+        <v>379</v>
+      </c>
       <c r="H73" s="1"/>
-      <c r="I73" s="6"/>
+      <c r="I73" s="1">
+        <v>379</v>
+      </c>
       <c r="J73" s="6"/>
       <c r="Q73" s="1">
-        <v>380.4</v>
+        <v>379.3</v>
       </c>
       <c r="R73" s="1">
-        <v>380.4</v>
-      </c>
-      <c r="S73" s="1" t="str">
+        <v>379.3</v>
+      </c>
+      <c r="S73" s="1">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T73" s="1" t="str">
+        <v>0.30000000000001137</v>
+      </c>
+      <c r="T73" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="U73" s="9" t="str">
+        <v>0.30000000000001137</v>
+      </c>
+      <c r="U73" s="9">
         <f t="shared" si="5"/>
-        <v/>
+        <v>7.9155672823221998E-4</v>
       </c>
       <c r="W73" s="1">
         <v>0</v>
@@ -4932,183 +5249,1265 @@
         <v>128</v>
       </c>
     </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>137</v>
-      </c>
-      <c r="E76" t="s">
-        <v>150</v>
-      </c>
-      <c r="I76">
-        <v>428</v>
-      </c>
-      <c r="R76">
-        <v>430</v>
-      </c>
-      <c r="S76" t="str">
-        <f>IF(AND(ISNUMBER(Q76),ISNUMBER(G76)),Q76-G76,"")</f>
-        <v/>
-      </c>
-      <c r="T76">
-        <f>IF(AND(ISNUMBER(R76),ISNUMBER(I76)),R76-I76,"")</f>
-        <v>2</v>
-      </c>
-      <c r="U76" s="10">
-        <f>IF(AND(ISNUMBER(R76),ISNUMBER(I76),I76&lt;&gt;0),(R76-I76)/I76,"")</f>
-        <v>4.6728971962616819E-3</v>
-      </c>
-      <c r="AE76" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+    <row r="74" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>167</v>
+      </c>
+      <c r="B74">
+        <v>200</v>
+      </c>
+      <c r="C74" s="1">
+        <v>100</v>
+      </c>
+      <c r="D74" s="1">
+        <v>0</v>
+      </c>
+      <c r="G74" s="1">
+        <v>29</v>
+      </c>
+      <c r="I74" s="1">
+        <v>29</v>
+      </c>
+      <c r="Q74">
+        <v>28.9</v>
+      </c>
+      <c r="R74">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>168</v>
+      </c>
+      <c r="B75" s="1">
+        <v>200</v>
+      </c>
+      <c r="C75" s="1">
+        <v>100</v>
+      </c>
+      <c r="D75" s="1">
+        <v>0</v>
+      </c>
+      <c r="G75" s="1">
         <v>139</v>
       </c>
-      <c r="E77" t="s">
-        <v>151</v>
-      </c>
-      <c r="I77">
-        <v>275</v>
-      </c>
-      <c r="J77">
-        <v>286</v>
-      </c>
-      <c r="R77">
-        <v>297</v>
-      </c>
-      <c r="S77" t="str">
-        <f>IF(AND(ISNUMBER(Q77),ISNUMBER(G77)),Q77-G77,"")</f>
-        <v/>
-      </c>
-      <c r="T77">
-        <f>IF(AND(ISNUMBER(R77),ISNUMBER(I77)),R77-I77,"")</f>
-        <v>22</v>
-      </c>
-      <c r="U77" s="10">
-        <f>IF(AND(ISNUMBER(R77),ISNUMBER(I77),I77&lt;&gt;0),(R77-I77)/I77,"")</f>
-        <v>0.08</v>
-      </c>
-      <c r="AE77" t="s">
-        <v>138</v>
+      <c r="I75">
+        <v>139</v>
+      </c>
+      <c r="Q75">
+        <v>139.30000000000001</v>
+      </c>
+      <c r="R75">
+        <v>139.30000000000001</v>
       </c>
     </row>
     <row r="78" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>140</v>
-      </c>
-      <c r="C78">
-        <v>27</v>
-      </c>
-      <c r="E78" t="s">
-        <v>152</v>
-      </c>
-      <c r="I78">
-        <v>381</v>
-      </c>
-      <c r="R78">
-        <v>393</v>
-      </c>
-      <c r="S78" t="str">
-        <f>IF(AND(ISNUMBER(Q78),ISNUMBER(G78)),Q78-G78,"")</f>
-        <v/>
-      </c>
-      <c r="T78">
-        <f>IF(AND(ISNUMBER(R78),ISNUMBER(I78)),R78-I78,"")</f>
-        <v>12</v>
-      </c>
-      <c r="U78" s="10">
-        <f>IF(AND(ISNUMBER(R78),ISNUMBER(I78),I78&lt;&gt;0),(R78-I78)/I78,"")</f>
-        <v>3.1496062992125984E-2</v>
-      </c>
-      <c r="AE78" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>141</v>
-      </c>
-      <c r="C79">
-        <v>27</v>
-      </c>
-      <c r="E79" t="s">
-        <v>152</v>
-      </c>
-      <c r="I79">
-        <v>695</v>
-      </c>
-      <c r="J79">
-        <v>728</v>
-      </c>
-      <c r="R79">
-        <v>706</v>
-      </c>
-      <c r="S79" t="str">
-        <f>IF(AND(ISNUMBER(Q79),ISNUMBER(G79)),Q79-G79,"")</f>
-        <v/>
-      </c>
-      <c r="T79">
-        <f>IF(AND(ISNUMBER(R79),ISNUMBER(I79)),R79-I79,"")</f>
-        <v>11</v>
-      </c>
-      <c r="U79" s="10">
-        <f>IF(AND(ISNUMBER(R79),ISNUMBER(I79),I79&lt;&gt;0),(R79-I79)/I79,"")</f>
-        <v>1.5827338129496403E-2</v>
-      </c>
-      <c r="AE79" t="s">
-        <v>138</v>
+      <c r="A78" s="18" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="80" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>142</v>
-      </c>
-      <c r="E80" t="s">
-        <v>153</v>
-      </c>
-      <c r="I80">
-        <v>323</v>
+        <v>167</v>
+      </c>
+      <c r="B80">
+        <v>200</v>
+      </c>
+      <c r="C80">
+        <v>10</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>25.8</v>
       </c>
       <c r="R80">
-        <v>326</v>
+        <v>25.8</v>
       </c>
       <c r="S80" t="str">
-        <f>IF(AND(ISNUMBER(Q80),ISNUMBER(G80)),Q80-G80,"")</f>
+        <f t="shared" ref="S80:S98" si="6">IF(AND(ISNUMBER(Q80),ISNUMBER(G80)),Q80-G80,"")</f>
         <v/>
       </c>
-      <c r="T80">
-        <f>IF(AND(ISNUMBER(R80),ISNUMBER(I80)),R80-I80,"")</f>
-        <v>3</v>
-      </c>
-      <c r="U80" s="10">
-        <f>IF(AND(ISNUMBER(R80),ISNUMBER(I80),I80&lt;&gt;0),(R80-I80)/I80,"")</f>
-        <v>9.2879256965944269E-3</v>
-      </c>
-      <c r="AE80" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" s="1"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="1"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="1"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="1"/>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="1"/>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E102" s="13"/>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" s="1"/>
+      <c r="T80" t="str">
+        <f t="shared" ref="T80:T98" si="7">IF(AND(ISNUMBER(R80),ISNUMBER(I80)),R80-I80,"")</f>
+        <v/>
+      </c>
+      <c r="U80" t="str">
+        <f t="shared" ref="U80:U98" si="8">IF(AND(ISNUMBER(R80),ISNUMBER(I80),I80&lt;&gt;0),(R80-I80)/I80,"")</f>
+        <v/>
+      </c>
+      <c r="AD80" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="81" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>167</v>
+      </c>
+      <c r="B81">
+        <v>200</v>
+      </c>
+      <c r="C81">
+        <v>20</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>25.5</v>
+      </c>
+      <c r="R81">
+        <v>25.5</v>
+      </c>
+      <c r="S81" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="T81" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="U81" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="AD81" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="82" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>167</v>
+      </c>
+      <c r="B82">
+        <v>200</v>
+      </c>
+      <c r="C82">
+        <v>40</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>26.3</v>
+      </c>
+      <c r="R82">
+        <v>26.3</v>
+      </c>
+      <c r="S82" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="T82" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="U82" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="AD82" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="83" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>167</v>
+      </c>
+      <c r="B83">
+        <v>200</v>
+      </c>
+      <c r="C83">
+        <v>60</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>27</v>
+      </c>
+      <c r="R83">
+        <v>27</v>
+      </c>
+      <c r="S83" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="T83" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="U83" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="AD83" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="84" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>167</v>
+      </c>
+      <c r="B84">
+        <v>200</v>
+      </c>
+      <c r="C84">
+        <v>80</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>27.2</v>
+      </c>
+      <c r="R84">
+        <v>27.2</v>
+      </c>
+      <c r="S84" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="T84" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="U84" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="AD84" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="85" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>168</v>
+      </c>
+      <c r="B85">
+        <v>200</v>
+      </c>
+      <c r="C85">
+        <v>10</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>1321.3</v>
+      </c>
+      <c r="R85">
+        <v>1321.3</v>
+      </c>
+      <c r="S85" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="T85" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="U85" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="AD85" t="s">
+        <v>176</v>
+      </c>
+      <c r="AE85" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="86" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>168</v>
+      </c>
+      <c r="B86">
+        <v>200</v>
+      </c>
+      <c r="C86">
+        <v>20</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <v>588</v>
+      </c>
+      <c r="R86">
+        <v>588</v>
+      </c>
+      <c r="S86" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="T86" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="U86" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="AD86" t="s">
+        <v>178</v>
+      </c>
+      <c r="AE86" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="87" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>168</v>
+      </c>
+      <c r="B87">
+        <v>200</v>
+      </c>
+      <c r="C87">
+        <v>40</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>284.7</v>
+      </c>
+      <c r="R87">
+        <v>284.7</v>
+      </c>
+      <c r="S87" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="T87" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="U87" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="AD87" t="s">
+        <v>180</v>
+      </c>
+      <c r="AE87" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="88" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>168</v>
+      </c>
+      <c r="B88">
+        <v>200</v>
+      </c>
+      <c r="C88">
+        <v>60</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="Q88">
+        <v>213.3</v>
+      </c>
+      <c r="R88">
+        <v>213.3</v>
+      </c>
+      <c r="S88" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="T88" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="U88" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="AD88" t="s">
+        <v>182</v>
+      </c>
+      <c r="AE88" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="89" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>168</v>
+      </c>
+      <c r="B89">
+        <v>200</v>
+      </c>
+      <c r="C89">
+        <v>80</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <v>201.8</v>
+      </c>
+      <c r="R89">
+        <v>201.8</v>
+      </c>
+      <c r="S89" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="T89" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="U89" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="AD89" t="s">
+        <v>184</v>
+      </c>
+      <c r="AE89" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="90" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B90">
+        <v>600</v>
+      </c>
+      <c r="C90">
+        <v>100</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="R90">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="S90" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="T90" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="U90" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="AD90" t="s">
+        <v>186</v>
+      </c>
+      <c r="AE90" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="91" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B91">
+        <v>600</v>
+      </c>
+      <c r="C91">
+        <v>100</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>400.5</v>
+      </c>
+      <c r="R91">
+        <v>400.5</v>
+      </c>
+      <c r="S91" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="T91" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="U91" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="AD91" t="s">
+        <v>186</v>
+      </c>
+      <c r="AE91" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="92" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B92">
+        <v>600</v>
+      </c>
+      <c r="C92">
+        <v>80</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>334</v>
+      </c>
+      <c r="R92">
+        <v>334</v>
+      </c>
+      <c r="S92" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="T92" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="U92" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="AD92" t="s">
+        <v>189</v>
+      </c>
+      <c r="AE92" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="93" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B93" t="s">
+        <v>25</v>
+      </c>
+      <c r="C93">
+        <v>8</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <v>54.6</v>
+      </c>
+      <c r="R93">
+        <v>49.2</v>
+      </c>
+      <c r="S93" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="T93" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="U93" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="AD93" t="s">
+        <v>192</v>
+      </c>
+      <c r="AE93" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="94" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B94" t="s">
+        <v>25</v>
+      </c>
+      <c r="C94">
+        <v>8</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <v>108.3</v>
+      </c>
+      <c r="R94">
+        <v>97.6</v>
+      </c>
+      <c r="S94" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="T94" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="U94" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="AD94" t="s">
+        <v>195</v>
+      </c>
+      <c r="AE94" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="95" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>197</v>
+      </c>
+      <c r="B95" t="s">
+        <v>25</v>
+      </c>
+      <c r="C95">
+        <v>8</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>607.79999999999995</v>
+      </c>
+      <c r="R95">
+        <v>117.2</v>
+      </c>
+      <c r="S95" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="T95" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="U95" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="AD95" t="s">
+        <v>198</v>
+      </c>
+      <c r="AE95" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="96" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>200</v>
+      </c>
+      <c r="B96" t="s">
+        <v>25</v>
+      </c>
+      <c r="C96">
+        <v>8</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96" s="13"/>
+      <c r="Q96">
+        <v>117.2</v>
+      </c>
+      <c r="R96">
+        <v>117.2</v>
+      </c>
+      <c r="S96" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="T96" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="U96" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="AD96" t="s">
+        <v>201</v>
+      </c>
+      <c r="AE96" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="97" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>203</v>
+      </c>
+      <c r="B97" t="s">
+        <v>25</v>
+      </c>
+      <c r="C97">
+        <v>8</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>184.5</v>
+      </c>
+      <c r="R97">
+        <v>184.5</v>
+      </c>
+      <c r="S97" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="T97" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="U97" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="AD97" t="s">
+        <v>204</v>
+      </c>
+      <c r="AE97" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="98" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B98">
+        <v>600</v>
+      </c>
+      <c r="C98" t="s">
+        <v>205</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="Q98">
+        <v>93.1</v>
+      </c>
+      <c r="R98">
+        <v>93.1</v>
+      </c>
+      <c r="S98" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="T98" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="U98" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="AD98" t="s">
+        <v>206</v>
+      </c>
+      <c r="AE98" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="100" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A100" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="AE100" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="101" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>31</v>
+      </c>
+      <c r="B101" t="s">
+        <v>25</v>
+      </c>
+      <c r="C101">
+        <v>8</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>100</v>
+      </c>
+      <c r="I101">
+        <v>100</v>
+      </c>
+      <c r="Q101">
+        <v>99.3</v>
+      </c>
+      <c r="R101">
+        <v>99.3</v>
+      </c>
+      <c r="S101">
+        <f>IF(AND(ISNUMBER(Q101),ISNUMBER(G101)),Q101-G101,"")</f>
+        <v>-0.70000000000000284</v>
+      </c>
+      <c r="T101">
+        <f>IF(AND(ISNUMBER(R101),ISNUMBER(I101)),R101-I101,"")</f>
+        <v>-0.70000000000000284</v>
+      </c>
+      <c r="U101">
+        <f>IF(AND(ISNUMBER(R101),ISNUMBER(I101),I101&lt;&gt;0),(R101-I101)/I101,"")</f>
+        <v>-7.0000000000000288E-3</v>
+      </c>
+      <c r="AD101" t="s">
+        <v>210</v>
+      </c>
+      <c r="AE101" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="102" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>99</v>
+      </c>
+      <c r="B102" t="s">
+        <v>25</v>
+      </c>
+      <c r="C102">
+        <v>8</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>146</v>
+      </c>
+      <c r="I102">
+        <v>146</v>
+      </c>
+      <c r="Q102">
+        <v>147</v>
+      </c>
+      <c r="R102">
+        <v>147</v>
+      </c>
+      <c r="S102">
+        <f>IF(AND(ISNUMBER(Q102),ISNUMBER(G102)),Q102-G102,"")</f>
+        <v>1</v>
+      </c>
+      <c r="T102">
+        <f>IF(AND(ISNUMBER(R102),ISNUMBER(I102)),R102-I102,"")</f>
+        <v>1</v>
+      </c>
+      <c r="U102">
+        <f>IF(AND(ISNUMBER(R102),ISNUMBER(I102),I102&lt;&gt;0),(R102-I102)/I102,"")</f>
+        <v>6.8493150684931503E-3</v>
+      </c>
+      <c r="AD102" t="s">
+        <v>212</v>
+      </c>
+      <c r="AE102" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="103" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>55</v>
+      </c>
+      <c r="B103">
+        <v>600</v>
+      </c>
+      <c r="C103">
+        <v>20</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>224</v>
+      </c>
+      <c r="I103">
+        <v>224</v>
+      </c>
+      <c r="Q103">
+        <v>224</v>
+      </c>
+      <c r="R103">
+        <v>224</v>
+      </c>
+      <c r="S103">
+        <f>IF(AND(ISNUMBER(Q103),ISNUMBER(G103)),Q103-G103,"")</f>
+        <v>0</v>
+      </c>
+      <c r="T103">
+        <f>IF(AND(ISNUMBER(R103),ISNUMBER(I103)),R103-I103,"")</f>
+        <v>0</v>
+      </c>
+      <c r="U103">
+        <f>IF(AND(ISNUMBER(R103),ISNUMBER(I103),I103&lt;&gt;0),(R103-I103)/I103,"")</f>
+        <v>0</v>
+      </c>
+      <c r="AD103" t="s">
+        <v>214</v>
+      </c>
+      <c r="AE103" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="104" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>73</v>
+      </c>
+      <c r="B104">
+        <v>600</v>
+      </c>
+      <c r="C104">
+        <v>100</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>300</v>
+      </c>
+      <c r="I104">
+        <v>300</v>
+      </c>
+      <c r="Q104">
+        <v>302.5</v>
+      </c>
+      <c r="R104">
+        <v>302.5</v>
+      </c>
+      <c r="S104">
+        <f>IF(AND(ISNUMBER(Q104),ISNUMBER(G104)),Q104-G104,"")</f>
+        <v>2.5</v>
+      </c>
+      <c r="T104">
+        <f>IF(AND(ISNUMBER(R104),ISNUMBER(I104)),R104-I104,"")</f>
+        <v>2.5</v>
+      </c>
+      <c r="U104">
+        <f>IF(AND(ISNUMBER(R104),ISNUMBER(I104),I104&lt;&gt;0),(R104-I104)/I104,"")</f>
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="AD104" t="s">
+        <v>216</v>
+      </c>
+      <c r="AE104" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="105" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>43</v>
+      </c>
+      <c r="B105" t="s">
+        <v>25</v>
+      </c>
+      <c r="C105">
+        <v>8</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>169</v>
+      </c>
+      <c r="I105">
+        <v>145</v>
+      </c>
+      <c r="Q105">
+        <v>144.1</v>
+      </c>
+      <c r="R105">
+        <v>144.1</v>
+      </c>
+      <c r="S105">
+        <f>IF(AND(ISNUMBER(Q105),ISNUMBER(G105)),Q105-G105,"")</f>
+        <v>-24.900000000000006</v>
+      </c>
+      <c r="T105">
+        <f>IF(AND(ISNUMBER(R105),ISNUMBER(I105)),R105-I105,"")</f>
+        <v>-0.90000000000000568</v>
+      </c>
+      <c r="U105">
+        <f>IF(AND(ISNUMBER(R105),ISNUMBER(I105),I105&lt;&gt;0),(R105-I105)/I105,"")</f>
+        <v>-6.2068965517241767E-3</v>
+      </c>
+      <c r="AD105" t="s">
+        <v>218</v>
+      </c>
+      <c r="AE105" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="107" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A107" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="AE107" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="108" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>31</v>
+      </c>
+      <c r="B108" t="s">
+        <v>25</v>
+      </c>
+      <c r="C108">
+        <v>8</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="Q108">
+        <v>99.3</v>
+      </c>
+      <c r="R108">
+        <v>99.3</v>
+      </c>
+      <c r="S108" t="str">
+        <f t="shared" ref="S108:S113" si="9">IF(AND(ISNUMBER(Q108),ISNUMBER(G108)),Q108-G108,"")</f>
+        <v/>
+      </c>
+      <c r="T108" t="str">
+        <f t="shared" ref="T108:T113" si="10">IF(AND(ISNUMBER(R108),ISNUMBER(I108)),R108-I108,"")</f>
+        <v/>
+      </c>
+      <c r="U108" t="str">
+        <f t="shared" ref="U108:U113" si="11">IF(AND(ISNUMBER(R108),ISNUMBER(I108),I108&lt;&gt;0),(R108-I108)/I108,"")</f>
+        <v/>
+      </c>
+      <c r="AD108" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="109" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>39</v>
+      </c>
+      <c r="B109" t="s">
+        <v>25</v>
+      </c>
+      <c r="C109">
+        <v>8</v>
+      </c>
+      <c r="D109">
+        <v>0</v>
+      </c>
+      <c r="Q109">
+        <v>85.6</v>
+      </c>
+      <c r="R109">
+        <v>85.6</v>
+      </c>
+      <c r="S109" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="T109" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="U109" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AD109" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="110" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>55</v>
+      </c>
+      <c r="B110">
+        <v>600</v>
+      </c>
+      <c r="C110">
+        <v>20</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+      <c r="Q110">
+        <v>224</v>
+      </c>
+      <c r="R110">
+        <v>224</v>
+      </c>
+      <c r="S110" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="T110" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="U110" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AD110" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="111" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>62</v>
+      </c>
+      <c r="B111">
+        <v>600</v>
+      </c>
+      <c r="C111">
+        <v>20</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="Q111">
+        <v>356.4</v>
+      </c>
+      <c r="R111">
+        <v>356.4</v>
+      </c>
+      <c r="S111" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="T111" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="U111" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AD111" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="112" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>57</v>
+      </c>
+      <c r="B112">
+        <v>600</v>
+      </c>
+      <c r="C112">
+        <v>20</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="Q112">
+        <v>894.1</v>
+      </c>
+      <c r="R112">
+        <v>894.1</v>
+      </c>
+      <c r="S112" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="T112" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="U112" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AD112" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="113" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>73</v>
+      </c>
+      <c r="B113">
+        <v>600</v>
+      </c>
+      <c r="C113">
+        <v>100</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="Q113">
+        <v>302.5</v>
+      </c>
+      <c r="R113">
+        <v>302.5</v>
+      </c>
+      <c r="S113" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="T113" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="U113" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AD113" t="s">
+        <v>227</v>
+      </c>
+      <c r="AE113" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="115" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A115" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="AE115" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="116" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>231</v>
+      </c>
+      <c r="B116" t="s">
+        <v>25</v>
+      </c>
+      <c r="C116">
+        <v>8</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="Q116">
+        <v>207.8</v>
+      </c>
+      <c r="R116">
+        <v>178.9</v>
+      </c>
+      <c r="S116" t="str">
+        <f>IF(AND(ISNUMBER(Q116),ISNUMBER(G116)),Q116-G116,"")</f>
+        <v/>
+      </c>
+      <c r="T116" t="str">
+        <f>IF(AND(ISNUMBER(R116),ISNUMBER(I116)),R116-I116,"")</f>
+        <v/>
+      </c>
+      <c r="U116" t="str">
+        <f>IF(AND(ISNUMBER(R116),ISNUMBER(I116),I116&lt;&gt;0),(R116-I116)/I116,"")</f>
+        <v/>
+      </c>
+      <c r="AD116" t="s">
+        <v>232</v>
+      </c>
+      <c r="AE116" t="s">
+        <v>233</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5120,8 +6519,1861 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D7DD02D-FFFE-4340-8BC5-E94FC1212CA4}">
+  <dimension ref="A1:AE121"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" customWidth="1"/>
+    <col min="3" max="3" width="7.44140625" customWidth="1"/>
+    <col min="4" max="4" width="8.109375" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" customWidth="1"/>
+    <col min="6" max="22" width="12.6640625" customWidth="1"/>
+    <col min="23" max="23" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="31" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="40" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="72.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="W1" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="X1" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y1" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z1" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA1" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB1" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC1" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE1" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="9"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="9"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="I4" s="6"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="9"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="1"/>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" t="s">
+        <v>149</v>
+      </c>
+      <c r="I5">
+        <v>428</v>
+      </c>
+      <c r="Q5">
+        <v>507</v>
+      </c>
+      <c r="R5">
+        <v>414.7</v>
+      </c>
+      <c r="S5" t="str">
+        <f>IF(AND(ISNUMBER(Q5),ISNUMBER(G5)),Q5-G5,"")</f>
+        <v/>
+      </c>
+      <c r="T5">
+        <f>IF(AND(ISNUMBER(R5),ISNUMBER(I5)),R5-I5,"")</f>
+        <v>-13.300000000000011</v>
+      </c>
+      <c r="U5" s="10">
+        <f>IF(AND(ISNUMBER(R5),ISNUMBER(I5),I5&lt;&gt;0),(R5-I5)/I5,"")</f>
+        <v>-3.1074766355140213E-2</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I6">
+        <v>275</v>
+      </c>
+      <c r="J6">
+        <v>286</v>
+      </c>
+      <c r="Q6">
+        <v>464.8</v>
+      </c>
+      <c r="R6">
+        <v>348</v>
+      </c>
+      <c r="S6" t="str">
+        <f>IF(AND(ISNUMBER(Q6),ISNUMBER(G6)),Q6-G6,"")</f>
+        <v/>
+      </c>
+      <c r="T6">
+        <f>IF(AND(ISNUMBER(R6),ISNUMBER(I6)),R6-I6,"")</f>
+        <v>73</v>
+      </c>
+      <c r="U6" s="10">
+        <f>IF(AND(ISNUMBER(R6),ISNUMBER(I6),I6&lt;&gt;0),(R6-I6)/I6,"")</f>
+        <v>0.26545454545454544</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I7">
+        <v>381</v>
+      </c>
+      <c r="Q7">
+        <v>430.8</v>
+      </c>
+      <c r="R7">
+        <v>380.1</v>
+      </c>
+      <c r="S7" t="str">
+        <f>IF(AND(ISNUMBER(Q7),ISNUMBER(G7)),Q7-G7,"")</f>
+        <v/>
+      </c>
+      <c r="T7">
+        <f>IF(AND(ISNUMBER(R7),ISNUMBER(I7)),R7-I7,"")</f>
+        <v>-0.89999999999997726</v>
+      </c>
+      <c r="U7" s="10">
+        <f>IF(AND(ISNUMBER(R7),ISNUMBER(I7),I7&lt;&gt;0),(R7-I7)/I7,"")</f>
+        <v>-2.3622047244093889E-3</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>151</v>
+      </c>
+      <c r="I8">
+        <v>695</v>
+      </c>
+      <c r="J8">
+        <v>728</v>
+      </c>
+      <c r="Q8">
+        <v>830.9</v>
+      </c>
+      <c r="R8">
+        <v>707.8</v>
+      </c>
+      <c r="S8" t="str">
+        <f>IF(AND(ISNUMBER(Q8),ISNUMBER(G8)),Q8-G8,"")</f>
+        <v/>
+      </c>
+      <c r="T8">
+        <f>IF(AND(ISNUMBER(R8),ISNUMBER(I8)),R8-I8,"")</f>
+        <v>12.799999999999955</v>
+      </c>
+      <c r="U8" s="10">
+        <f>IF(AND(ISNUMBER(R8),ISNUMBER(I8),I8&lt;&gt;0),(R8-I8)/I8,"")</f>
+        <v>1.8417266187050294E-2</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E9" t="s">
+        <v>152</v>
+      </c>
+      <c r="I9">
+        <v>323</v>
+      </c>
+      <c r="S9" t="str">
+        <f>IF(AND(ISNUMBER(Q9),ISNUMBER(G9)),Q9-G9,"")</f>
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <f>IF(AND(ISNUMBER(R9),ISNUMBER(I9)),R9-I9,"")</f>
+        <v/>
+      </c>
+      <c r="U9" s="10" t="str">
+        <f>IF(AND(ISNUMBER(R9),ISNUMBER(I9),I9&lt;&gt;0),(R9-I9)/I9,"")</f>
+        <v/>
+      </c>
+      <c r="AE9" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="I10" s="6"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="9"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="1"/>
+      <c r="AD10" s="1"/>
+      <c r="AE10" s="1"/>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="I11" s="6"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="9"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="1"/>
+      <c r="AD11" s="1"/>
+      <c r="AE11" s="1"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="I12" s="6"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="9"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1"/>
+      <c r="AA12" s="1"/>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="1"/>
+      <c r="AD12" s="1"/>
+      <c r="AE12" s="1"/>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="I13" s="6"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="9"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1"/>
+      <c r="Y13" s="1"/>
+      <c r="Z13" s="1"/>
+      <c r="AA13" s="1"/>
+      <c r="AB13" s="1"/>
+      <c r="AC13" s="1"/>
+      <c r="AD13" s="1"/>
+      <c r="AE13" s="1"/>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="I14" s="6"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="9"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1"/>
+      <c r="Z14" s="1"/>
+      <c r="AA14" s="1"/>
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="1"/>
+      <c r="AD14" s="1"/>
+      <c r="AE14" s="1"/>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="I15" s="6"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="9"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1"/>
+      <c r="AA15" s="1"/>
+      <c r="AB15" s="1"/>
+      <c r="AC15" s="1"/>
+      <c r="AD15" s="1"/>
+      <c r="AE15" s="1"/>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="I16" s="6"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="9"/>
+      <c r="W16" s="1"/>
+      <c r="X16" s="1"/>
+      <c r="Y16" s="1"/>
+      <c r="Z16" s="1"/>
+      <c r="AA16" s="1"/>
+      <c r="AB16" s="1"/>
+      <c r="AC16" s="1"/>
+      <c r="AD16" s="1"/>
+      <c r="AE16" s="1"/>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="9"/>
+      <c r="W17" s="1"/>
+      <c r="X17" s="1"/>
+      <c r="Y17" s="1"/>
+      <c r="Z17" s="1"/>
+      <c r="AA17" s="1"/>
+      <c r="AB17" s="1"/>
+      <c r="AC17" s="1"/>
+      <c r="AD17" s="1"/>
+      <c r="AE17" s="1"/>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="9"/>
+      <c r="W18" s="1"/>
+      <c r="X18" s="1"/>
+      <c r="Y18" s="1"/>
+      <c r="Z18" s="1"/>
+      <c r="AA18" s="1"/>
+      <c r="AB18" s="1"/>
+      <c r="AC18" s="1"/>
+      <c r="AD18" s="1"/>
+      <c r="AE18" s="1"/>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="9"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="1"/>
+      <c r="AA19" s="1"/>
+      <c r="AB19" s="1"/>
+      <c r="AC19" s="1"/>
+      <c r="AD19" s="1"/>
+      <c r="AE19" s="1"/>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="9"/>
+      <c r="W20" s="1"/>
+      <c r="X20" s="1"/>
+      <c r="Y20" s="1"/>
+      <c r="Z20" s="1"/>
+      <c r="AA20" s="1"/>
+      <c r="AB20" s="1"/>
+      <c r="AC20" s="1"/>
+      <c r="AD20" s="1"/>
+      <c r="AE20" s="1"/>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="9"/>
+      <c r="W21" s="1"/>
+      <c r="X21" s="1"/>
+      <c r="Y21" s="1"/>
+      <c r="Z21" s="1"/>
+      <c r="AA21" s="1"/>
+      <c r="AB21" s="1"/>
+      <c r="AC21" s="1"/>
+      <c r="AD21" s="1"/>
+      <c r="AE21" s="1"/>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="9"/>
+      <c r="W22" s="1"/>
+      <c r="X22" s="1"/>
+      <c r="Y22" s="1"/>
+      <c r="Z22" s="1"/>
+      <c r="AA22" s="1"/>
+      <c r="AB22" s="1"/>
+      <c r="AC22" s="1"/>
+      <c r="AD22" s="1"/>
+      <c r="AE22" s="1"/>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="9"/>
+      <c r="W23" s="1"/>
+      <c r="X23" s="1"/>
+      <c r="Y23" s="1"/>
+      <c r="Z23" s="1"/>
+      <c r="AA23" s="1"/>
+      <c r="AB23" s="1"/>
+      <c r="AC23" s="1"/>
+      <c r="AD23" s="1"/>
+      <c r="AE23" s="1"/>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="9"/>
+      <c r="W24" s="1"/>
+      <c r="X24" s="1"/>
+      <c r="Y24" s="1"/>
+      <c r="Z24" s="1"/>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1"/>
+      <c r="AC24" s="1"/>
+      <c r="AD24" s="1"/>
+      <c r="AE24" s="1"/>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="9"/>
+      <c r="W25" s="1"/>
+      <c r="X25" s="1"/>
+      <c r="Y25" s="1"/>
+      <c r="Z25" s="1"/>
+      <c r="AA25" s="1"/>
+      <c r="AB25" s="1"/>
+      <c r="AC25" s="1"/>
+      <c r="AD25" s="1"/>
+      <c r="AE25" s="1"/>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="9"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="1"/>
+      <c r="Y26" s="1"/>
+      <c r="Z26" s="1"/>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="1"/>
+      <c r="AC26" s="1"/>
+      <c r="AD26" s="1"/>
+      <c r="AE26" s="1"/>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="9"/>
+      <c r="W27" s="1"/>
+      <c r="X27" s="1"/>
+      <c r="Y27" s="1"/>
+      <c r="Z27" s="1"/>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="1"/>
+      <c r="AC27" s="1"/>
+      <c r="AD27" s="1"/>
+      <c r="AE27" s="1"/>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="9"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
+      <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="1"/>
+      <c r="AC28" s="1"/>
+      <c r="AD28" s="1"/>
+      <c r="AE28" s="1"/>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="9"/>
+      <c r="W29" s="1"/>
+      <c r="X29" s="1"/>
+      <c r="Y29" s="1"/>
+      <c r="Z29" s="1"/>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="1"/>
+      <c r="AC29" s="1"/>
+      <c r="AD29" s="1"/>
+      <c r="AE29" s="1"/>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="9"/>
+      <c r="W30" s="1"/>
+      <c r="X30" s="1"/>
+      <c r="Y30" s="1"/>
+      <c r="Z30" s="1"/>
+      <c r="AA30" s="1"/>
+      <c r="AB30" s="1"/>
+      <c r="AC30" s="1"/>
+      <c r="AD30" s="1"/>
+      <c r="AE30" s="1"/>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="9"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
+      <c r="AB31" s="1"/>
+      <c r="AC31" s="1"/>
+      <c r="AD31" s="1"/>
+      <c r="AE31" s="1"/>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="9"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
+      <c r="AB32" s="1"/>
+      <c r="AC32" s="1"/>
+      <c r="AD32" s="1"/>
+      <c r="AE32" s="1"/>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="9"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1"/>
+      <c r="Y33" s="1"/>
+      <c r="Z33" s="1"/>
+      <c r="AA33" s="1"/>
+      <c r="AB33" s="1"/>
+      <c r="AC33" s="1"/>
+      <c r="AD33" s="1"/>
+      <c r="AE33" s="1"/>
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="9"/>
+      <c r="W34" s="1"/>
+      <c r="X34" s="1"/>
+      <c r="Y34" s="1"/>
+      <c r="Z34" s="1"/>
+      <c r="AA34" s="1"/>
+      <c r="AB34" s="1"/>
+      <c r="AC34" s="1"/>
+      <c r="AD34" s="1"/>
+      <c r="AE34" s="1"/>
+    </row>
+    <row r="35" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="9"/>
+      <c r="W35" s="1"/>
+      <c r="X35" s="1"/>
+      <c r="Y35" s="1"/>
+      <c r="Z35" s="1"/>
+      <c r="AA35" s="1"/>
+      <c r="AB35" s="1"/>
+      <c r="AC35" s="1"/>
+      <c r="AD35" s="1"/>
+      <c r="AE35" s="1"/>
+    </row>
+    <row r="36" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="9"/>
+      <c r="W36" s="1"/>
+      <c r="X36" s="1"/>
+      <c r="Y36" s="1"/>
+      <c r="Z36" s="1"/>
+      <c r="AA36" s="1"/>
+      <c r="AB36" s="1"/>
+      <c r="AC36" s="1"/>
+      <c r="AD36" s="1"/>
+      <c r="AE36" s="1"/>
+    </row>
+    <row r="37" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="9"/>
+      <c r="W37" s="1"/>
+      <c r="X37" s="1"/>
+      <c r="Y37" s="1"/>
+      <c r="Z37" s="1"/>
+      <c r="AA37" s="1"/>
+      <c r="AB37" s="1"/>
+      <c r="AC37" s="1"/>
+      <c r="AD37" s="1"/>
+      <c r="AE37" s="1"/>
+    </row>
+    <row r="38" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="9"/>
+      <c r="W38" s="1"/>
+      <c r="X38" s="1"/>
+      <c r="Y38" s="1"/>
+      <c r="Z38" s="1"/>
+      <c r="AA38" s="1"/>
+      <c r="AB38" s="1"/>
+      <c r="AC38" s="1"/>
+      <c r="AD38" s="1"/>
+      <c r="AE38" s="1"/>
+    </row>
+    <row r="39" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="1"/>
+      <c r="U39" s="9"/>
+      <c r="W39" s="1"/>
+      <c r="X39" s="1"/>
+      <c r="Y39" s="1"/>
+      <c r="Z39" s="1"/>
+      <c r="AA39" s="1"/>
+      <c r="AB39" s="1"/>
+      <c r="AC39" s="1"/>
+      <c r="AD39" s="1"/>
+      <c r="AE39" s="1"/>
+    </row>
+    <row r="40" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="Q40" s="1"/>
+      <c r="R40" s="1"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="1"/>
+      <c r="U40" s="9"/>
+      <c r="W40" s="1"/>
+      <c r="X40" s="1"/>
+      <c r="Y40" s="1"/>
+      <c r="Z40" s="1"/>
+      <c r="AA40" s="1"/>
+      <c r="AB40" s="1"/>
+      <c r="AC40" s="1"/>
+      <c r="AD40" s="1"/>
+      <c r="AE40" s="1"/>
+    </row>
+    <row r="41" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="Q41" s="1"/>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1"/>
+      <c r="U41" s="9"/>
+      <c r="W41" s="1"/>
+      <c r="X41" s="1"/>
+      <c r="Y41" s="1"/>
+      <c r="Z41" s="1"/>
+      <c r="AA41" s="1"/>
+      <c r="AB41" s="1"/>
+      <c r="AC41" s="1"/>
+      <c r="AD41" s="1"/>
+      <c r="AE41" s="1"/>
+    </row>
+    <row r="42" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="Q42" s="1"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="9"/>
+      <c r="W42" s="1"/>
+      <c r="X42" s="1"/>
+      <c r="Y42" s="1"/>
+      <c r="Z42" s="1"/>
+      <c r="AA42" s="1"/>
+      <c r="AB42" s="1"/>
+      <c r="AC42" s="1"/>
+      <c r="AD42" s="1"/>
+      <c r="AE42" s="1"/>
+    </row>
+    <row r="43" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="Q43" s="1"/>
+      <c r="R43" s="1"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="9"/>
+      <c r="W43" s="1"/>
+      <c r="X43" s="1"/>
+      <c r="Y43" s="1"/>
+      <c r="Z43" s="1"/>
+      <c r="AA43" s="1"/>
+      <c r="AB43" s="1"/>
+      <c r="AC43" s="1"/>
+      <c r="AD43" s="1"/>
+      <c r="AE43" s="1"/>
+    </row>
+    <row r="44" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="9"/>
+      <c r="W44" s="1"/>
+      <c r="X44" s="1"/>
+      <c r="Y44" s="1"/>
+      <c r="Z44" s="1"/>
+      <c r="AA44" s="1"/>
+      <c r="AB44" s="1"/>
+      <c r="AC44" s="1"/>
+      <c r="AD44" s="1"/>
+      <c r="AE44" s="1"/>
+    </row>
+    <row r="45" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="G45" s="7"/>
+      <c r="I45" s="8"/>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="9"/>
+      <c r="W45" s="1"/>
+      <c r="X45" s="1"/>
+      <c r="Y45" s="1"/>
+      <c r="Z45" s="1"/>
+      <c r="AA45" s="1"/>
+      <c r="AB45" s="1"/>
+      <c r="AC45" s="1"/>
+      <c r="AD45" s="1"/>
+      <c r="AE45" s="1"/>
+    </row>
+    <row r="46" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="Q46" s="1"/>
+      <c r="R46" s="1"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="1"/>
+      <c r="U46" s="9"/>
+      <c r="W46" s="1"/>
+      <c r="X46" s="1"/>
+      <c r="Y46" s="1"/>
+      <c r="Z46" s="1"/>
+      <c r="AA46" s="1"/>
+      <c r="AB46" s="1"/>
+      <c r="AC46" s="1"/>
+      <c r="AD46" s="1"/>
+      <c r="AE46" s="1"/>
+    </row>
+    <row r="47" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
+      <c r="U47" s="9"/>
+      <c r="W47" s="1"/>
+      <c r="X47" s="1"/>
+      <c r="Y47" s="1"/>
+      <c r="Z47" s="1"/>
+      <c r="AA47" s="1"/>
+      <c r="AB47" s="1"/>
+      <c r="AC47" s="1"/>
+      <c r="AD47" s="1"/>
+      <c r="AE47" s="1"/>
+    </row>
+    <row r="48" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="1"/>
+      <c r="U48" s="9"/>
+      <c r="W48" s="1"/>
+      <c r="X48" s="1"/>
+      <c r="Y48" s="1"/>
+      <c r="Z48" s="1"/>
+      <c r="AA48" s="1"/>
+      <c r="AB48" s="1"/>
+      <c r="AC48" s="1"/>
+      <c r="AD48" s="1"/>
+      <c r="AE48" s="1"/>
+    </row>
+    <row r="51" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="J51" s="6"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="9"/>
+      <c r="W51" s="1"/>
+      <c r="X51" s="1"/>
+      <c r="Y51" s="1"/>
+      <c r="Z51" s="1"/>
+      <c r="AA51" s="1"/>
+      <c r="AB51" s="1"/>
+      <c r="AC51" s="1"/>
+      <c r="AD51" s="1"/>
+      <c r="AE51" s="1"/>
+    </row>
+    <row r="52" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="Q52" s="1"/>
+      <c r="R52" s="1"/>
+      <c r="S52" s="1"/>
+      <c r="T52" s="1"/>
+      <c r="U52" s="9"/>
+      <c r="W52" s="1"/>
+      <c r="X52" s="1"/>
+      <c r="Y52" s="1"/>
+      <c r="Z52" s="1"/>
+      <c r="AA52" s="1"/>
+      <c r="AB52" s="1"/>
+      <c r="AC52" s="1"/>
+      <c r="AD52" s="1"/>
+      <c r="AE52" s="1"/>
+    </row>
+    <row r="53" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+      <c r="Q53" s="1"/>
+      <c r="R53" s="1"/>
+      <c r="S53" s="1"/>
+      <c r="T53" s="1"/>
+      <c r="U53" s="9"/>
+      <c r="W53" s="1"/>
+      <c r="X53" s="1"/>
+      <c r="Y53" s="1"/>
+      <c r="Z53" s="1"/>
+      <c r="AA53" s="1"/>
+      <c r="AB53" s="1"/>
+      <c r="AC53" s="1"/>
+      <c r="AD53" s="1"/>
+      <c r="AE53" s="1"/>
+    </row>
+    <row r="54" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="Q54" s="1"/>
+      <c r="R54" s="1"/>
+      <c r="S54" s="1"/>
+      <c r="T54" s="1"/>
+      <c r="U54" s="9"/>
+      <c r="W54" s="1"/>
+      <c r="X54" s="1"/>
+      <c r="Y54" s="1"/>
+      <c r="Z54" s="1"/>
+      <c r="AA54" s="1"/>
+      <c r="AB54" s="1"/>
+      <c r="AC54" s="1"/>
+      <c r="AD54" s="1"/>
+      <c r="AE54" s="1"/>
+    </row>
+    <row r="55" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="6"/>
+      <c r="Q55" s="1"/>
+      <c r="R55" s="1"/>
+      <c r="S55" s="1"/>
+      <c r="T55" s="1"/>
+      <c r="U55" s="9"/>
+      <c r="W55" s="1"/>
+      <c r="X55" s="1"/>
+      <c r="Y55" s="1"/>
+      <c r="Z55" s="1"/>
+      <c r="AA55" s="1"/>
+      <c r="AB55" s="1"/>
+      <c r="AC55" s="1"/>
+      <c r="AD55" s="1"/>
+      <c r="AE55" s="1"/>
+    </row>
+    <row r="56" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="Q56" s="1"/>
+      <c r="R56" s="1"/>
+      <c r="S56" s="1"/>
+      <c r="T56" s="1"/>
+      <c r="U56" s="9"/>
+      <c r="W56" s="1"/>
+      <c r="X56" s="1"/>
+      <c r="Y56" s="1"/>
+      <c r="Z56" s="1"/>
+      <c r="AA56" s="1"/>
+      <c r="AB56" s="1"/>
+      <c r="AC56" s="1"/>
+      <c r="AD56" s="1"/>
+      <c r="AE56" s="1"/>
+    </row>
+    <row r="57" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+      <c r="Q57" s="1"/>
+      <c r="R57" s="1"/>
+      <c r="S57" s="1"/>
+      <c r="T57" s="1"/>
+      <c r="U57" s="9"/>
+      <c r="W57" s="1"/>
+      <c r="X57" s="1"/>
+      <c r="Y57" s="1"/>
+      <c r="Z57" s="1"/>
+      <c r="AA57" s="1"/>
+      <c r="AB57" s="1"/>
+      <c r="AC57" s="1"/>
+      <c r="AD57" s="1"/>
+      <c r="AE57" s="1"/>
+    </row>
+    <row r="58" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+      <c r="Q58" s="1"/>
+      <c r="R58" s="1"/>
+      <c r="S58" s="1"/>
+      <c r="T58" s="1"/>
+      <c r="U58" s="9"/>
+      <c r="W58" s="1"/>
+      <c r="X58" s="1"/>
+      <c r="Y58" s="1"/>
+      <c r="Z58" s="1"/>
+      <c r="AA58" s="1"/>
+      <c r="AB58" s="1"/>
+      <c r="AC58" s="1"/>
+      <c r="AD58" s="1"/>
+      <c r="AE58" s="1"/>
+    </row>
+    <row r="59" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="Q59" s="1"/>
+      <c r="R59" s="1"/>
+      <c r="S59" s="1"/>
+      <c r="T59" s="1"/>
+      <c r="U59" s="9"/>
+      <c r="W59" s="1"/>
+      <c r="X59" s="1"/>
+      <c r="Y59" s="1"/>
+      <c r="Z59" s="1"/>
+      <c r="AA59" s="1"/>
+      <c r="AB59" s="1"/>
+      <c r="AC59" s="1"/>
+      <c r="AD59" s="1"/>
+      <c r="AE59" s="1"/>
+    </row>
+    <row r="60" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="Q60" s="1"/>
+      <c r="R60" s="1"/>
+      <c r="S60" s="1"/>
+      <c r="T60" s="1"/>
+      <c r="U60" s="9"/>
+      <c r="W60" s="1"/>
+      <c r="X60" s="1"/>
+      <c r="Y60" s="1"/>
+      <c r="Z60" s="1"/>
+      <c r="AA60" s="1"/>
+      <c r="AB60" s="1"/>
+      <c r="AC60" s="1"/>
+      <c r="AD60" s="1"/>
+      <c r="AE60" s="1"/>
+    </row>
+    <row r="61" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="6"/>
+      <c r="Q61" s="1"/>
+      <c r="R61" s="1"/>
+      <c r="S61" s="1"/>
+      <c r="T61" s="1"/>
+      <c r="U61" s="9"/>
+      <c r="W61" s="1"/>
+      <c r="X61" s="1"/>
+      <c r="Y61" s="1"/>
+      <c r="Z61" s="1"/>
+      <c r="AA61" s="1"/>
+      <c r="AB61" s="1"/>
+      <c r="AC61" s="1"/>
+      <c r="AD61" s="1"/>
+      <c r="AE61" s="1"/>
+    </row>
+    <row r="62" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+      <c r="Q62" s="1"/>
+      <c r="R62" s="1"/>
+      <c r="S62" s="1"/>
+      <c r="T62" s="1"/>
+      <c r="U62" s="9"/>
+      <c r="W62" s="1"/>
+      <c r="X62" s="1"/>
+      <c r="Y62" s="1"/>
+      <c r="Z62" s="1"/>
+      <c r="AA62" s="1"/>
+      <c r="AB62" s="1"/>
+      <c r="AC62" s="1"/>
+      <c r="AD62" s="1"/>
+      <c r="AE62" s="1"/>
+    </row>
+    <row r="63" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+      <c r="Q63" s="1"/>
+      <c r="R63" s="1"/>
+      <c r="S63" s="1"/>
+      <c r="T63" s="1"/>
+      <c r="U63" s="9"/>
+      <c r="W63" s="1"/>
+      <c r="X63" s="1"/>
+      <c r="Y63" s="1"/>
+      <c r="Z63" s="1"/>
+      <c r="AA63" s="1"/>
+      <c r="AB63" s="1"/>
+      <c r="AC63" s="1"/>
+      <c r="AD63" s="1"/>
+      <c r="AE63" s="1"/>
+    </row>
+    <row r="64" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
+      <c r="Q64" s="1"/>
+      <c r="R64" s="1"/>
+      <c r="S64" s="1"/>
+      <c r="T64" s="1"/>
+      <c r="U64" s="9"/>
+      <c r="W64" s="1"/>
+      <c r="X64" s="1"/>
+      <c r="Y64" s="1"/>
+      <c r="Z64" s="1"/>
+      <c r="AA64" s="1"/>
+      <c r="AB64" s="1"/>
+      <c r="AC64" s="1"/>
+      <c r="AD64" s="1"/>
+      <c r="AE64" s="1"/>
+    </row>
+    <row r="65" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
+      <c r="Q65" s="1"/>
+      <c r="R65" s="1"/>
+      <c r="S65" s="1"/>
+      <c r="T65" s="1"/>
+      <c r="U65" s="9"/>
+      <c r="W65" s="1"/>
+      <c r="X65" s="1"/>
+      <c r="Y65" s="1"/>
+      <c r="Z65" s="1"/>
+      <c r="AA65" s="1"/>
+      <c r="AB65" s="1"/>
+      <c r="AC65" s="1"/>
+      <c r="AD65" s="1"/>
+      <c r="AE65" s="1"/>
+    </row>
+    <row r="66" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="Q66" s="1"/>
+      <c r="R66" s="1"/>
+      <c r="S66" s="1"/>
+      <c r="T66" s="1"/>
+      <c r="U66" s="9"/>
+      <c r="W66" s="1"/>
+      <c r="X66" s="1"/>
+      <c r="Y66" s="1"/>
+      <c r="Z66" s="1"/>
+      <c r="AA66" s="1"/>
+      <c r="AB66" s="1"/>
+      <c r="AC66" s="1"/>
+      <c r="AD66" s="1"/>
+      <c r="AE66" s="1"/>
+    </row>
+    <row r="67" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
+      <c r="Q67" s="1"/>
+      <c r="R67" s="1"/>
+      <c r="S67" s="1"/>
+      <c r="T67" s="1"/>
+      <c r="U67" s="9"/>
+      <c r="W67" s="1"/>
+      <c r="X67" s="1"/>
+      <c r="Y67" s="1"/>
+      <c r="Z67" s="1"/>
+      <c r="AA67" s="1"/>
+      <c r="AB67" s="1"/>
+      <c r="AC67" s="1"/>
+      <c r="AD67" s="1"/>
+      <c r="AE67" s="1"/>
+    </row>
+    <row r="68" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="6"/>
+      <c r="Q68" s="1"/>
+      <c r="R68" s="1"/>
+      <c r="S68" s="1"/>
+      <c r="T68" s="1"/>
+      <c r="U68" s="9"/>
+      <c r="W68" s="1"/>
+      <c r="X68" s="1"/>
+      <c r="Y68" s="1"/>
+      <c r="Z68" s="1"/>
+      <c r="AA68" s="1"/>
+      <c r="AB68" s="1"/>
+      <c r="AC68" s="1"/>
+      <c r="AD68" s="1"/>
+      <c r="AE68" s="1"/>
+    </row>
+    <row r="69" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
+      <c r="Q69" s="1"/>
+      <c r="R69" s="1"/>
+      <c r="S69" s="1"/>
+      <c r="T69" s="1"/>
+      <c r="U69" s="9"/>
+      <c r="W69" s="1"/>
+      <c r="X69" s="1"/>
+      <c r="Y69" s="1"/>
+      <c r="Z69" s="1"/>
+      <c r="AA69" s="1"/>
+      <c r="AB69" s="1"/>
+      <c r="AC69" s="1"/>
+      <c r="AD69" s="1"/>
+      <c r="AE69" s="1"/>
+    </row>
+    <row r="70" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="6"/>
+      <c r="J70" s="6"/>
+      <c r="Q70" s="1"/>
+      <c r="R70" s="1"/>
+      <c r="S70" s="1"/>
+      <c r="T70" s="1"/>
+      <c r="U70" s="9"/>
+      <c r="W70" s="1"/>
+      <c r="X70" s="1"/>
+      <c r="Y70" s="1"/>
+      <c r="Z70" s="1"/>
+      <c r="AA70" s="1"/>
+      <c r="AB70" s="1"/>
+      <c r="AC70" s="1"/>
+      <c r="AD70" s="1"/>
+      <c r="AE70" s="1"/>
+    </row>
+    <row r="71" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="6"/>
+      <c r="J71" s="6"/>
+      <c r="Q71" s="1"/>
+      <c r="R71" s="1"/>
+      <c r="S71" s="1"/>
+      <c r="T71" s="1"/>
+      <c r="U71" s="9"/>
+      <c r="W71" s="1"/>
+      <c r="X71" s="1"/>
+      <c r="Y71" s="1"/>
+      <c r="Z71" s="1"/>
+      <c r="AA71" s="1"/>
+      <c r="AB71" s="1"/>
+      <c r="AC71" s="1"/>
+      <c r="AD71" s="1"/>
+      <c r="AE71" s="1"/>
+    </row>
+    <row r="72" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="6"/>
+      <c r="Q72" s="1"/>
+      <c r="R72" s="1"/>
+      <c r="S72" s="1"/>
+      <c r="T72" s="1"/>
+      <c r="U72" s="9"/>
+      <c r="W72" s="1"/>
+      <c r="X72" s="1"/>
+      <c r="Y72" s="1"/>
+      <c r="Z72" s="1"/>
+      <c r="AA72" s="1"/>
+      <c r="AB72" s="1"/>
+      <c r="AC72" s="1"/>
+      <c r="AD72" s="1"/>
+      <c r="AE72" s="1"/>
+    </row>
+    <row r="73" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="6"/>
+      <c r="Q73" s="1"/>
+      <c r="R73" s="1"/>
+      <c r="S73" s="1"/>
+      <c r="T73" s="1"/>
+      <c r="U73" s="9"/>
+      <c r="W73" s="1"/>
+      <c r="X73" s="1"/>
+      <c r="Y73" s="1"/>
+      <c r="Z73" s="1"/>
+      <c r="AA73" s="1"/>
+      <c r="AB73" s="1"/>
+      <c r="AC73" s="1"/>
+      <c r="AD73" s="1"/>
+      <c r="AE73" s="1"/>
+    </row>
+    <row r="74" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="I74" s="1"/>
+    </row>
+    <row r="75" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="G75" s="1"/>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" s="18"/>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" s="1"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="1"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="1"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="1"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" s="1"/>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E102" s="13"/>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" s="1"/>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" s="18"/>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" s="18"/>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="18" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13F92E11-B679-4D3F-BE48-D002695F10FF}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -5134,7 +8386,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B2" s="16">
         <v>120</v>
@@ -5149,17 +8401,17 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>147</v>
       </c>
       <c r="D3">
         <f>IFERROR(VALUE(LEFT(B3,FIND(":",B3)-1))*60+VALUE(MID(B3,FIND(":",B3)+1,9)),"")</f>
-        <v>72</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -5167,7 +8419,7 @@
         <v>131</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -5177,7 +8429,7 @@
         <v>132</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -5187,7 +8439,7 @@
         <v>133</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -5197,7 +8449,7 @@
         <v>134</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -5207,7 +8459,7 @@
         <v>135</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -5217,7 +8469,7 @@
         <v>136</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -5233,7 +8485,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -5243,7 +8495,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -5253,7 +8505,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -5263,7 +8515,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -5273,10 +8525,15 @@
         <v>14</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>166</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
